--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3198" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3198" uniqueCount="491">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1206,13 +1206,16 @@
     <t>Need to refer to a particular code in the system.</t>
   </si>
   <si>
+    <t>63653004</t>
+  </si>
+  <si>
     <t>Coding.code</t>
   </si>
   <si>
     <t>./code</t>
   </si>
   <si>
-    <t>1393: fixed value = 63653004</t>
+    <t>1393: fixed value = #63653004</t>
   </si>
   <si>
     <t>Device.type.coding.display</t>
@@ -8281,7 +8284,7 @@
         <v>78</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>78</v>
+        <v>379</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>78</v>
@@ -8320,7 +8323,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8335,7 +8338,7 @@
         <v>98</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>78</v>
@@ -8344,7 +8347,7 @@
         <v>78</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>78</v>
@@ -8352,10 +8355,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8381,14 +8384,14 @@
         <v>152</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>78</v>
@@ -8437,7 +8440,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8452,7 +8455,7 @@
         <v>98</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>78</v>
@@ -8469,10 +8472,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8495,19 +8498,19 @@
         <v>87</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>78</v>
@@ -8556,7 +8559,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8571,7 +8574,7 @@
         <v>98</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>78</v>
@@ -8588,10 +8591,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8617,16 +8620,16 @@
         <v>152</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>78</v>
@@ -8675,7 +8678,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8690,7 +8693,7 @@
         <v>98</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>78</v>
@@ -8707,10 +8710,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8736,10 +8739,10 @@
         <v>217</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8790,7 +8793,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8822,10 +8825,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8937,10 +8940,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9054,10 +9057,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9173,10 +9176,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9202,10 +9205,10 @@
         <v>174</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9256,7 +9259,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>86</v>
@@ -9288,10 +9291,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9317,10 +9320,10 @@
         <v>152</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9371,7 +9374,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9403,10 +9406,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9432,10 +9435,10 @@
         <v>217</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9486,7 +9489,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9518,10 +9521,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9633,10 +9636,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9750,10 +9753,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9869,10 +9872,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9898,10 +9901,10 @@
         <v>174</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9952,7 +9955,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9984,10 +9987,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10013,10 +10016,10 @@
         <v>144</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10067,7 +10070,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10099,10 +10102,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10128,10 +10131,10 @@
         <v>152</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10182,7 +10185,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>86</v>
@@ -10214,10 +10217,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10243,10 +10246,10 @@
         <v>217</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10297,7 +10300,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10329,10 +10332,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10444,10 +10447,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10561,10 +10564,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10680,10 +10683,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10709,10 +10712,10 @@
         <v>174</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10763,7 +10766,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>86</v>
@@ -10795,10 +10798,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10821,13 +10824,13 @@
         <v>78</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10878,7 +10881,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -10910,10 +10913,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10939,10 +10942,10 @@
         <v>174</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -10993,7 +10996,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11025,10 +11028,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11051,17 +11054,17 @@
         <v>78</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>78</v>
@@ -11110,7 +11113,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11125,27 +11128,27 @@
         <v>98</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11171,10 +11174,10 @@
         <v>206</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11225,7 +11228,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11240,10 +11243,10 @@
         <v>98</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>78</v>
@@ -11257,10 +11260,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11283,16 +11286,16 @@
         <v>78</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11342,7 +11345,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11357,10 +11360,10 @@
         <v>98</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>78</v>
@@ -11374,10 +11377,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11400,17 +11403,17 @@
         <v>78</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>78</v>
@@ -11459,7 +11462,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -11474,10 +11477,10 @@
         <v>98</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>78</v>
@@ -11491,10 +11494,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11520,13 +11523,13 @@
         <v>100</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -11576,7 +11579,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -11591,10 +11594,10 @@
         <v>98</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>78</v>
@@ -11608,10 +11611,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11634,13 +11637,13 @@
         <v>78</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -11691,7 +11694,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -11706,7 +11709,7 @@
         <v>98</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AL84" t="s" s="2">
         <v>78</v>
@@ -11723,10 +11726,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11752,10 +11755,10 @@
         <v>174</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11806,7 +11809,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -11838,10 +11841,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11864,13 +11867,13 @@
         <v>78</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -11921,7 +11924,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$75</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3198" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2789" uniqueCount="439">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1112,174 +1112,22 @@
     <t>The kind or type of device.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://snomed.info/sct"/&gt;
+    &lt;code value="63653004"/&gt;
+    &lt;display value="Biomedical device"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>Codes to identify medical devices</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/device-kind</t>
   </si>
   <si>
-    <t>Device.type.id</t>
-  </si>
-  <si>
-    <t>Device.type.extension</t>
-  </si>
-  <si>
-    <t>Device.type.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>Device.type.coding.id</t>
-  </si>
-  <si>
-    <t>Device.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Device.type.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>Device.type.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>Device.type.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>63653004</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>1393: fixed value = #63653004</t>
-  </si>
-  <si>
-    <t>Device.type.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>Device.type.coding.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Device.type.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
+    <t>1393: fixed value = http://snomed.info/sct#63653004 Biomedical device</t>
   </si>
   <si>
     <t>Device.specialization</t>
@@ -1889,7 +1737,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO86"/>
+  <dimension ref="A1:AO75"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="37.6015625" customWidth="true" bestFit="true"/>
@@ -7348,7 +7196,7 @@
         <v>78</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>78</v>
+        <v>348</v>
       </c>
       <c r="T47" t="s" s="2">
         <v>78</v>
@@ -7366,10 +7214,10 @@
         <v>179</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>78</v>
@@ -7411,7 +7259,7 @@
         <v>78</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>78</v>
+        <v>351</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>78</v>
@@ -7419,10 +7267,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7433,7 +7281,7 @@
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>78</v>
@@ -7445,13 +7293,13 @@
         <v>78</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>152</v>
+        <v>217</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>153</v>
+        <v>353</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>154</v>
+        <v>354</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7502,22 +7350,22 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>155</v>
+        <v>352</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>156</v>
+        <v>78</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>78</v>
@@ -7534,21 +7382,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>131</v>
+        <v>78</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>78</v>
@@ -7560,17 +7408,15 @@
         <v>78</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>135</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>78</v>
@@ -7607,31 +7453,31 @@
         <v>78</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>160</v>
+        <v>78</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>161</v>
+        <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>156</v>
@@ -7651,14 +7497,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7674,23 +7520,21 @@
         <v>78</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>353</v>
+        <v>132</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>354</v>
+        <v>133</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>355</v>
+        <v>158</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>357</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>78</v>
       </c>
@@ -7738,7 +7582,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>358</v>
+        <v>162</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7750,10 +7594,10 @@
         <v>78</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>359</v>
+        <v>156</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>78</v>
@@ -7770,42 +7614,46 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>78</v>
+        <v>225</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>153</v>
+        <v>226</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>78</v>
       </c>
@@ -7853,22 +7701,22 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>155</v>
+        <v>228</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>156</v>
+        <v>129</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>78</v>
@@ -7885,21 +7733,21 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>131</v>
+        <v>325</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>78</v>
@@ -7911,17 +7759,15 @@
         <v>78</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>132</v>
+        <v>174</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>133</v>
+        <v>359</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>135</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>78</v>
@@ -7958,34 +7804,34 @@
         <v>78</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>160</v>
+        <v>78</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>161</v>
+        <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>162</v>
+        <v>358</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>156</v>
+        <v>78</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>78</v>
@@ -8002,10 +7848,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8025,23 +7871,19 @@
         <v>78</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>100</v>
+        <v>152</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="M53" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>366</v>
-      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>78</v>
       </c>
@@ -8089,7 +7931,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8104,10 +7946,10 @@
         <v>98</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>368</v>
+        <v>78</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>78</v>
+        <v>234</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>78</v>
@@ -8121,10 +7963,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8135,7 +7977,7 @@
         <v>79</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>78</v>
@@ -8144,20 +7986,18 @@
         <v>78</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>152</v>
+        <v>217</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>372</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>78</v>
@@ -8206,13 +8046,13 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>78</v>
@@ -8221,7 +8061,7 @@
         <v>98</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>374</v>
+        <v>78</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>78</v>
@@ -8238,10 +8078,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8255,27 +8095,25 @@
         <v>86</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>106</v>
+        <v>152</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>376</v>
+        <v>153</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>377</v>
+        <v>154</v>
       </c>
       <c r="N55" s="2"/>
-      <c r="O55" t="s" s="2">
-        <v>378</v>
-      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>78</v>
       </c>
@@ -8284,7 +8122,7 @@
         <v>78</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>379</v>
+        <v>78</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>78</v>
@@ -8323,7 +8161,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>380</v>
+        <v>155</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8335,10 +8173,10 @@
         <v>78</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>381</v>
+        <v>156</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>78</v>
@@ -8347,7 +8185,7 @@
         <v>78</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>382</v>
+        <v>78</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>78</v>
@@ -8355,21 +8193,21 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>78</v>
@@ -8378,21 +8216,21 @@
         <v>78</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>384</v>
+        <v>133</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" t="s" s="2">
-        <v>386</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>78</v>
       </c>
@@ -8440,22 +8278,22 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>387</v>
+        <v>162</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>388</v>
+        <v>156</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>78</v>
@@ -8472,45 +8310,45 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>389</v>
+        <v>369</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>389</v>
+        <v>369</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>78</v>
+        <v>225</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="J57" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>390</v>
+        <v>132</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>391</v>
+        <v>226</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>392</v>
+        <v>227</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>393</v>
+        <v>135</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>394</v>
+        <v>141</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>78</v>
@@ -8559,22 +8397,22 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>395</v>
+        <v>228</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>396</v>
+        <v>129</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>78</v>
@@ -8591,14 +8429,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>397</v>
+        <v>370</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>397</v>
+        <v>370</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>78</v>
+        <v>325</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8614,23 +8452,19 @@
         <v>78</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>398</v>
+        <v>371</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>401</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>78</v>
       </c>
@@ -8678,7 +8512,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>402</v>
+        <v>370</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8693,7 +8527,7 @@
         <v>98</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>403</v>
+        <v>78</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>78</v>
@@ -8710,10 +8544,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>404</v>
+        <v>373</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>404</v>
+        <v>373</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8724,7 +8558,7 @@
         <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>78</v>
@@ -8736,13 +8570,13 @@
         <v>78</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>217</v>
+        <v>144</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>405</v>
+        <v>374</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>406</v>
+        <v>375</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8793,13 +8627,13 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>404</v>
+        <v>373</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>78</v>
@@ -8811,7 +8645,7 @@
         <v>78</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>78</v>
+        <v>234</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>78</v>
@@ -8825,10 +8659,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>407</v>
+        <v>376</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>407</v>
+        <v>376</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8836,7 +8670,7 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>86</v>
@@ -8854,10 +8688,10 @@
         <v>152</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>153</v>
+        <v>377</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>154</v>
+        <v>378</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8908,10 +8742,10 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>155</v>
+        <v>376</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>86</v>
@@ -8920,10 +8754,10 @@
         <v>78</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>156</v>
+        <v>78</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>78</v>
@@ -8940,14 +8774,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>408</v>
+        <v>379</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>408</v>
+        <v>379</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>131</v>
+        <v>78</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -8966,17 +8800,15 @@
         <v>78</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>132</v>
+        <v>217</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>133</v>
+        <v>380</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>135</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>78</v>
@@ -9025,7 +8857,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>162</v>
+        <v>379</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9037,10 +8869,10 @@
         <v>78</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>156</v>
+        <v>78</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>78</v>
@@ -9057,46 +8889,42 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>409</v>
+        <v>382</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>409</v>
+        <v>382</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>225</v>
+        <v>78</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>226</v>
+        <v>153</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>78</v>
       </c>
@@ -9144,22 +8972,22 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>228</v>
+        <v>155</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>78</v>
@@ -9176,21 +9004,21 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>410</v>
+        <v>383</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>410</v>
+        <v>383</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>325</v>
+        <v>131</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>78</v>
@@ -9202,15 +9030,17 @@
         <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>174</v>
+        <v>132</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>411</v>
+        <v>133</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>158</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>135</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>78</v>
@@ -9259,22 +9089,22 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>410</v>
+        <v>162</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>78</v>
@@ -9291,42 +9121,46 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>413</v>
+        <v>384</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>413</v>
+        <v>384</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>78</v>
+        <v>225</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>414</v>
+        <v>226</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>78</v>
       </c>
@@ -9374,25 +9208,25 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>413</v>
+        <v>228</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>234</v>
+        <v>78</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>78</v>
@@ -9406,10 +9240,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>416</v>
+        <v>385</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>416</v>
+        <v>385</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9417,10 +9251,10 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>78</v>
@@ -9432,13 +9266,13 @@
         <v>78</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>217</v>
+        <v>174</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>417</v>
+        <v>386</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>418</v>
+        <v>387</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9489,13 +9323,13 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>416</v>
+        <v>385</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>78</v>
@@ -9521,10 +9355,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>419</v>
+        <v>388</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>419</v>
+        <v>388</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9535,7 +9369,7 @@
         <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>78</v>
@@ -9547,13 +9381,13 @@
         <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>152</v>
+        <v>389</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>153</v>
+        <v>390</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>154</v>
+        <v>391</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9604,22 +9438,22 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>155</v>
+        <v>388</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>156</v>
+        <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>78</v>
@@ -9636,14 +9470,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>420</v>
+        <v>392</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>420</v>
+        <v>392</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>131</v>
+        <v>78</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9662,17 +9496,15 @@
         <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>132</v>
+        <v>174</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>133</v>
+        <v>393</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>135</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>78</v>
@@ -9721,7 +9553,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>162</v>
+        <v>392</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9733,10 +9565,10 @@
         <v>78</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>156</v>
+        <v>78</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>78</v>
@@ -9753,45 +9585,43 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>421</v>
+        <v>395</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>421</v>
+        <v>395</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>225</v>
+        <v>78</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>132</v>
+        <v>396</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>226</v>
+        <v>397</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>135</v>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>141</v>
+        <v>399</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>78</v>
@@ -9840,46 +9670,46 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>228</v>
+        <v>395</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>129</v>
+        <v>400</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>78</v>
+        <v>401</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>78</v>
+        <v>402</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>78</v>
+        <v>403</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>422</v>
+        <v>404</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>422</v>
+        <v>404</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>325</v>
+        <v>78</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -9898,13 +9728,13 @@
         <v>78</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>423</v>
+        <v>405</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9955,7 +9785,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>422</v>
+        <v>404</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9970,10 +9800,10 @@
         <v>98</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>78</v>
+        <v>407</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>78</v>
+        <v>408</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>78</v>
@@ -9987,10 +9817,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>425</v>
+        <v>409</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>425</v>
+        <v>409</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10001,7 +9831,7 @@
         <v>79</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>78</v>
@@ -10013,15 +9843,17 @@
         <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>144</v>
+        <v>410</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>412</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>413</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>78</v>
@@ -10070,13 +9902,13 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>425</v>
+        <v>409</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>78</v>
@@ -10085,10 +9917,10 @@
         <v>98</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>78</v>
+        <v>414</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>234</v>
+        <v>408</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>78</v>
@@ -10102,10 +9934,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10113,7 +9945,7 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>86</v>
@@ -10128,16 +9960,18 @@
         <v>78</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>152</v>
+        <v>416</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
+      <c r="O71" t="s" s="2">
+        <v>419</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
       </c>
@@ -10185,10 +10019,10 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>86</v>
@@ -10200,10 +10034,10 @@
         <v>98</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>78</v>
+        <v>420</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>78</v>
+        <v>421</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>78</v>
@@ -10217,10 +10051,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10231,7 +10065,7 @@
         <v>79</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>78</v>
@@ -10243,15 +10077,17 @@
         <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>217</v>
+        <v>100</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>424</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>425</v>
+      </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>78</v>
@@ -10300,13 +10136,13 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>78</v>
@@ -10315,10 +10151,10 @@
         <v>98</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>78</v>
+        <v>426</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>78</v>
+        <v>421</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>78</v>
@@ -10332,10 +10168,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10346,7 +10182,7 @@
         <v>79</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>78</v>
@@ -10358,13 +10194,13 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>152</v>
+        <v>428</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>153</v>
+        <v>429</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>154</v>
+        <v>430</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10415,22 +10251,22 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>155</v>
+        <v>427</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>156</v>
+        <v>431</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>78</v>
@@ -10447,14 +10283,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>131</v>
+        <v>78</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10470,20 +10306,18 @@
         <v>78</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>132</v>
+        <v>174</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>133</v>
+        <v>433</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>135</v>
-      </c>
+        <v>434</v>
+      </c>
+      <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>78</v>
@@ -10532,7 +10366,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>162</v>
+        <v>432</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10544,10 +10378,10 @@
         <v>78</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>156</v>
+        <v>266</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>78</v>
@@ -10564,46 +10398,42 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>225</v>
+        <v>78</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>132</v>
+        <v>436</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>226</v>
+        <v>437</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>438</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>78</v>
       </c>
@@ -10651,22 +10481,22 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>228</v>
+        <v>435</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>129</v>
+        <v>78</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>78</v>
@@ -10678,1284 +10508,11 @@
         <v>78</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="76" hidden="true">
-      <c r="A76" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="C76" s="2"/>
-      <c r="D76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E76" s="2"/>
-      <c r="F76" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="G76" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K76" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="L76" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
-      <c r="P76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q76" s="2"/>
-      <c r="R76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="77" hidden="true">
-      <c r="A77" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="C77" s="2"/>
-      <c r="D77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E77" s="2"/>
-      <c r="F77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K77" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
-      <c r="P77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q77" s="2"/>
-      <c r="R77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="AG77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ77" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="78" hidden="true">
-      <c r="A78" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="C78" s="2"/>
-      <c r="D78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E78" s="2"/>
-      <c r="F78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K78" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="L78" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
-      <c r="P78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q78" s="2"/>
-      <c r="R78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="AG78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ78" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO78" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="79" hidden="true">
-      <c r="A79" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="C79" s="2"/>
-      <c r="D79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E79" s="2"/>
-      <c r="F79" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="G79" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H79" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="I79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K79" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="L79" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="N79" s="2"/>
-      <c r="O79" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="P79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q79" s="2"/>
-      <c r="R79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="AG79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH79" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ79" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK79" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="AO79" t="s" s="2">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="80" hidden="true">
-      <c r="A80" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="C80" s="2"/>
-      <c r="D80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E80" s="2"/>
-      <c r="F80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G80" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K80" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="L80" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
-      <c r="P80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q80" s="2"/>
-      <c r="R80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="AG80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH80" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ80" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK80" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO80" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="81" hidden="true">
-      <c r="A81" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="C81" s="2"/>
-      <c r="D81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E81" s="2"/>
-      <c r="F81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K81" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="O81" s="2"/>
-      <c r="P81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q81" s="2"/>
-      <c r="R81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="AG81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ81" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK81" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="82" hidden="true">
-      <c r="A82" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="C82" s="2"/>
-      <c r="D82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E82" s="2"/>
-      <c r="F82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G82" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K82" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="L82" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N82" s="2"/>
-      <c r="O82" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="P82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q82" s="2"/>
-      <c r="R82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ82" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK82" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="83" hidden="true">
-      <c r="A83" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="C83" s="2"/>
-      <c r="D83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E83" s="2"/>
-      <c r="F83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G83" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K83" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="O83" s="2"/>
-      <c r="P83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q83" s="2"/>
-      <c r="R83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="AG83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH83" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ83" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK83" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="84" hidden="true">
-      <c r="A84" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="C84" s="2"/>
-      <c r="D84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E84" s="2"/>
-      <c r="F84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K84" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="L84" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
-      <c r="P84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q84" s="2"/>
-      <c r="R84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="AG84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ84" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="85" hidden="true">
-      <c r="A85" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="B85" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="C85" s="2"/>
-      <c r="D85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E85" s="2"/>
-      <c r="F85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J85" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="K85" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="L85" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="N85" s="2"/>
-      <c r="O85" s="2"/>
-      <c r="P85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q85" s="2"/>
-      <c r="R85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="AG85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ85" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK85" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="AL85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO85" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="86" hidden="true">
-      <c r="A86" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="C86" s="2"/>
-      <c r="D86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E86" s="2"/>
-      <c r="F86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G86" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K86" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="L86" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N86" s="2"/>
-      <c r="O86" s="2"/>
-      <c r="P86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q86" s="2"/>
-      <c r="R86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="AG86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH86" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ86" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO86" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO86">
+  <autoFilter ref="A1:AO75">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11965,7 +10522,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI85">
+  <conditionalFormatting sqref="A2:AI74">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1285,33 +1285,7 @@
     <t>1399: reference from SURGERY - PATIENT (#130-.01)</t>
   </si>
   <si>
-    <t>Surg.AnesthesiaAgent.PatientIEN
-Surg.AnesthesiaBlockSite.PatientIEN
-Surg.AnesthesiaTechnique.PatientIEN
-Surg.AnesthesiaTestDose.PatientIEN
-Surg.ReferringPhysician.PatientIEN
-Surg.ReplacementFluidType.PatientIEN
-Surg.SurgeryAssistant.PatientIEN
-Surg.SurgeryAssistantOther.PatientIEN
-Surg.SurgeryDelay.PatientIEN
-Surg.SurgeryINTRA.PatientIEN
-Surg.SurgeryIrrigation.PatientIEN
-Surg.SurgeryMedication.PatientIEN
-Surg.SurgeryOccurrenceNonOp.PatientIEN
-Surg.SurgeryOtherProcedure.PatientIEN
-Surg.SurgeryOtherProcedureCPTModifier.PatientIEN
-Surg.SurgeryOtherProcedureDiagnosis.PatientIEN
-Surg.SurgeryPostOpDiagnosis.PatientIEN
-Surg.SurgeryPreOpDiagnosis.PatientIEN
-Surg.SurgeryPrincipalDiagnosis.PatientIEN
-Surg.SurgeryProcedureCPTModifier.PatientIEN
-Surg.SurgeryProcedureOccurrence.PatientIEN
-Surg.SurgeryRequiredBloodProducts.PatientIEN
-Surg.SurgeryReturnCase.PatientIEN
-Surg.SurgORCircSupport.PatientIEN
-Surg.SurgORCircSupportTime.PatientIEN
-Surg.SurgORScrubSupport.PatientIEN
-Surg.SurgORScrubSupportTime.PatientIEN</t>
+    <t>Surg.AnesthesiaAgent.PatientIEN,Surg.AnesthesiaBlockSite.PatientIEN,Surg.AnesthesiaTechnique.PatientIEN,Surg.AnesthesiaTestDose.PatientIEN,Surg.ReferringPhysician.PatientIEN,Surg.ReplacementFluidType.PatientIEN,Surg.SurgeryAssistant.PatientIEN,Surg.SurgeryAssistantOther.PatientIEN,Surg.SurgeryDelay.PatientIEN,Surg.SurgeryINTRA.PatientIEN,Surg.SurgeryIrrigation.PatientIEN,Surg.SurgeryMedication.PatientIEN,Surg.SurgeryOccurrenceNonOp.PatientIEN,Surg.SurgeryOtherProcedure.PatientIEN,Surg.SurgeryOtherProcedureCPTModifier.PatientIEN,Surg.SurgeryOtherProcedureDiagnosis.PatientIEN,Surg.SurgeryPostOpDiagnosis.PatientIEN,Surg.SurgeryPreOpDiagnosis.PatientIEN,Surg.SurgeryPrincipalDiagnosis.PatientIEN,Surg.SurgeryProcedureCPTModifier.PatientIEN,Surg.SurgeryProcedureOccurrence.PatientIEN,Surg.SurgeryRequiredBloodProducts.PatientIEN,Surg.SurgeryReturnCase.PatientIEN,Surg.SurgORCircSupport.PatientIEN,Surg.SurgORCircSupportTime.PatientIEN,Surg.SurgORScrubSupport.PatientIEN,Surg.SurgORScrubSupportTime.PatientIEN</t>
   </si>
   <si>
     <t>Device.owner</t>
@@ -1779,7 +1753,7 @@
     <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="111.0546875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="49.28125" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,6 +237,12 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
     <t>Mapping: RIM Mapping</t>
   </si>
   <si>
@@ -244,12 +250,6 @@
   </si>
   <si>
     <t>Mapping: UDI Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
     <t/>
@@ -628,10 +628,10 @@
     <t>Identifier.value</t>
   </si>
   <si>
+    <t>1348: source value from PROSTHESIS INSTALLED - IEN (#130.01-.001)</t>
+  </si>
+  <si>
     <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
-  </si>
-  <si>
-    <t>1348: source value from PROSTHESIS INSTALLED - IEN (#130.01-.001)</t>
   </si>
   <si>
     <t>Device.identifier.period</t>
@@ -935,13 +935,13 @@
     <t>A name of the manufacturer.</t>
   </si>
   <si>
+    <t>1365: source value from PROSTHESIS INSTALLED - VENDOR (#130.01-1)</t>
+  </si>
+  <si>
+    <t>SPatient.ImplantedProsthesis.ProsthesisVendor</t>
+  </si>
+  <si>
     <t>.playedRole[typeCode=MANU].scoper.name</t>
-  </si>
-  <si>
-    <t>1365: source value from PROSTHESIS INSTALLED - VENDOR (#130.01-1)</t>
-  </si>
-  <si>
-    <t>SPatient.ImplantedProsthesis.ProsthesisVendor</t>
   </si>
   <si>
     <t>Device.manufactureDate</t>
@@ -972,18 +972,18 @@
     <t>The date and time beyond which this device is no longer valid or should not be used (if applicable).</t>
   </si>
   <si>
+    <t>1373: source value from PROSTHESIS INSTALLED - STERILITY EXPIRATION DATE (#130.01-9)</t>
+  </si>
+  <si>
+    <t>SPatient.ImplantedProsthesis.SterilityExpirationDate</t>
+  </si>
+  <si>
     <t>.expirationTime</t>
   </si>
   <si>
     <t>the expiration date of a specific device -  which is a component of the production identifier (PI), a conditional, variable portion of a UDI.  For FHIR, The datetime syntax must converted to YYYY-MM-DD[THH:MM:SS].  If hour is present, the minutes and seconds should both be set to “00”.</t>
   </si>
   <si>
-    <t>1373: source value from PROSTHESIS INSTALLED - STERILITY EXPIRATION DATE (#130.01-9)</t>
-  </si>
-  <si>
-    <t>SPatient.ImplantedProsthesis.SterilityExpirationDate</t>
-  </si>
-  <si>
     <t>Device.lotNumber</t>
   </si>
   <si>
@@ -1011,13 +1011,13 @@
     <t>Alphanumeric Maximum 20.</t>
   </si>
   <si>
+    <t>1379: source value from PROSTHESIS INSTALLED - SERIAL NUMBER (#130.01-12)</t>
+  </si>
+  <si>
+    <t>SPatient.ImplantedProsthesis.SerialNumber</t>
+  </si>
+  <si>
     <t>.playedRole[typeCode=MANU].id</t>
-  </si>
-  <si>
-    <t>1379: source value from PROSTHESIS INSTALLED - SERIAL NUMBER (#130.01-12)</t>
-  </si>
-  <si>
-    <t>SPatient.ImplantedProsthesis.SerialNumber</t>
   </si>
   <si>
     <t>Device.deviceName</t>
@@ -1085,13 +1085,13 @@
     <t>The model number for the device.</t>
   </si>
   <si>
+    <t>1387: source value from PROSTHESIS INSTALLED - MODEL (#130.01-2)</t>
+  </si>
+  <si>
+    <t>SPatient.ImplantedProsthesis.ProsthesisModel</t>
+  </si>
+  <si>
     <t>.softwareName (included as part)</t>
-  </si>
-  <si>
-    <t>1387: source value from PROSTHESIS INSTALLED - MODEL (#130.01-2)</t>
-  </si>
-  <si>
-    <t>SPatient.ImplantedProsthesis.ProsthesisModel</t>
   </si>
   <si>
     <t>Device.partNumber</t>
@@ -1276,16 +1276,16 @@
     <t>If the device is implanted in a patient, then need to associate the device to the patient.</t>
   </si>
   <si>
+    <t>1399: reference from SURGERY - PATIENT (#130-.01)</t>
+  </si>
+  <si>
+    <t>Surg.AnesthesiaAgent.PatientIEN,Surg.AnesthesiaBlockSite.PatientIEN,Surg.AnesthesiaTechnique.PatientIEN,Surg.AnesthesiaTestDose.PatientIEN,Surg.ReferringPhysician.PatientIEN,Surg.ReplacementFluidType.PatientIEN,Surg.SurgeryAssistant.PatientIEN,Surg.SurgeryAssistantOther.PatientIEN,Surg.SurgeryDelay.PatientIEN,Surg.SurgeryINTRA.PatientIEN,Surg.SurgeryIrrigation.PatientIEN,Surg.SurgeryMedication.PatientIEN,Surg.SurgeryOccurrenceNonOp.PatientIEN,Surg.SurgeryOtherProcedure.PatientIEN,Surg.SurgeryOtherProcedureCPTModifier.PatientIEN,Surg.SurgeryOtherProcedureDiagnosis.PatientIEN,Surg.SurgeryPostOpDiagnosis.PatientIEN,Surg.SurgeryPreOpDiagnosis.PatientIEN,Surg.SurgeryPrincipalDiagnosis.PatientIEN,Surg.SurgeryProcedureCPTModifier.PatientIEN,Surg.SurgeryProcedureOccurrence.PatientIEN,Surg.SurgeryRequiredBloodProducts.PatientIEN,Surg.SurgeryReturnCase.PatientIEN,Surg.SurgORCircSupport.PatientIEN,Surg.SurgORCircSupportTime.PatientIEN,Surg.SurgORScrubSupport.PatientIEN,Surg.SurgORScrubSupportTime.PatientIEN</t>
+  </si>
+  <si>
     <t>.playedRole[typeCode=USED].scoper.playedRole[typeCode=PAT]</t>
   </si>
   <si>
     <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>1399: reference from SURGERY - PATIENT (#130-.01)</t>
-  </si>
-  <si>
-    <t>Surg.AnesthesiaAgent.PatientIEN,Surg.AnesthesiaBlockSite.PatientIEN,Surg.AnesthesiaTechnique.PatientIEN,Surg.AnesthesiaTestDose.PatientIEN,Surg.ReferringPhysician.PatientIEN,Surg.ReplacementFluidType.PatientIEN,Surg.SurgeryAssistant.PatientIEN,Surg.SurgeryAssistantOther.PatientIEN,Surg.SurgeryDelay.PatientIEN,Surg.SurgeryINTRA.PatientIEN,Surg.SurgeryIrrigation.PatientIEN,Surg.SurgeryMedication.PatientIEN,Surg.SurgeryOccurrenceNonOp.PatientIEN,Surg.SurgeryOtherProcedure.PatientIEN,Surg.SurgeryOtherProcedureCPTModifier.PatientIEN,Surg.SurgeryOtherProcedureDiagnosis.PatientIEN,Surg.SurgeryPostOpDiagnosis.PatientIEN,Surg.SurgeryPreOpDiagnosis.PatientIEN,Surg.SurgeryPrincipalDiagnosis.PatientIEN,Surg.SurgeryProcedureCPTModifier.PatientIEN,Surg.SurgeryProcedureOccurrence.PatientIEN,Surg.SurgeryRequiredBloodProducts.PatientIEN,Surg.SurgeryReturnCase.PatientIEN,Surg.SurgORCircSupport.PatientIEN,Surg.SurgORCircSupportTime.PatientIEN,Surg.SurgORScrubSupport.PatientIEN,Surg.SurgORScrubSupportTime.PatientIEN</t>
   </si>
   <si>
     <t>Device.owner</t>
@@ -1749,10 +1749,10 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="102.6171875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="111.0546875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="111.0546875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="102.6171875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -1983,13 +1983,13 @@
         <v>84</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM2" t="s" s="2">
         <v>30</v>
-      </c>
-      <c r="AL2" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM2" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN2" t="s" s="2">
         <v>78</v>
@@ -2566,13 +2566,13 @@
         <v>98</v>
       </c>
       <c r="AK7" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL7" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM7" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN7" t="s" s="2">
         <v>78</v>
@@ -2683,13 +2683,13 @@
         <v>78</v>
       </c>
       <c r="AK8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM8" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="AL8" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM8" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>78</v>
@@ -2800,13 +2800,13 @@
         <v>137</v>
       </c>
       <c r="AK9" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL9" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM9" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="AL9" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM9" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>78</v>
@@ -2919,13 +2919,13 @@
         <v>137</v>
       </c>
       <c r="AK10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM10" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="AL10" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM10" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>78</v>
@@ -3036,19 +3036,19 @@
         <v>98</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AO11" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="AN11" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="12" hidden="true">
@@ -3151,13 +3151,13 @@
         <v>78</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM12" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>78</v>
@@ -3268,13 +3268,13 @@
         <v>137</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>78</v>
@@ -3387,13 +3387,13 @@
         <v>98</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>78</v>
@@ -3506,13 +3506,13 @@
         <v>98</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM15" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>78</v>
@@ -3625,13 +3625,13 @@
         <v>98</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM16" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM16" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>78</v>
@@ -3748,10 +3748,10 @@
         <v>78</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>78</v>
+        <v>198</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>78</v>
@@ -3857,13 +3857,13 @@
         <v>98</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>78</v>
@@ -3974,13 +3974,13 @@
         <v>98</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>78</v>
@@ -4206,16 +4206,16 @@
         <v>98</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AL21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>78</v>
@@ -4321,13 +4321,13 @@
         <v>78</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AL22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>78</v>
@@ -4438,13 +4438,13 @@
         <v>137</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>78</v>
@@ -4557,13 +4557,13 @@
         <v>137</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>78</v>
@@ -4672,19 +4672,19 @@
         <v>98</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="26" hidden="true">
@@ -4787,19 +4787,19 @@
         <v>98</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="AL26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO26" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="27" hidden="true">
@@ -4904,13 +4904,13 @@
         <v>98</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>78</v>
@@ -5021,19 +5021,19 @@
         <v>98</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="AL28" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO28" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="29" hidden="true">
@@ -5138,19 +5138,19 @@
         <v>98</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="AL29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM29" t="s" s="2">
+      <c r="AN29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO29" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="30" hidden="true">
@@ -5255,13 +5255,13 @@
         <v>98</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>78</v>
@@ -5372,16 +5372,16 @@
         <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="AL31" t="s" s="2">
+      <c r="AN31" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>78</v>
@@ -5490,13 +5490,13 @@
         <v>78</v>
       </c>
       <c r="AL32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>78</v>
@@ -5604,19 +5604,19 @@
         <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AL33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AO33" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="34" hidden="true">
@@ -5722,16 +5722,16 @@
         <v>290</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>292</v>
       </c>
     </row>
     <row r="35" hidden="true">
@@ -5834,19 +5834,19 @@
         <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="AL35" t="s" s="2">
+      <c r="AN35" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="AM35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="36" hidden="true">
@@ -5952,13 +5952,13 @@
         <v>302</v>
       </c>
       <c r="AL36" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>305</v>
@@ -6064,19 +6064,19 @@
         <v>98</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AL37" t="s" s="2">
+      <c r="AN37" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>310</v>
       </c>
     </row>
     <row r="38" hidden="true">
@@ -6184,16 +6184,16 @@
         <v>315</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="AM38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>316</v>
-      </c>
       <c r="AO38" t="s" s="2">
-        <v>317</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39" hidden="true">
@@ -6411,13 +6411,13 @@
         <v>78</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>78</v>
@@ -6528,13 +6528,13 @@
         <v>137</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>78</v>
@@ -6647,13 +6647,13 @@
         <v>137</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>78</v>
@@ -6762,19 +6762,19 @@
         <v>98</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>78</v>
+        <v>328</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>78</v>
+        <v>329</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>328</v>
+        <v>78</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>329</v>
+        <v>78</v>
       </c>
     </row>
     <row r="44" hidden="true">
@@ -6877,16 +6877,16 @@
         <v>98</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="AL44" t="s" s="2">
+      <c r="AN44" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>78</v>
@@ -6995,16 +6995,16 @@
         <v>339</v>
       </c>
       <c r="AL45" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="AM45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>340</v>
-      </c>
       <c r="AO45" t="s" s="2">
-        <v>341</v>
+        <v>78</v>
       </c>
     </row>
     <row r="46" hidden="true">
@@ -7109,16 +7109,16 @@
         <v>98</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>315</v>
+        <v>78</v>
       </c>
       <c r="AL46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AN46" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>78</v>
@@ -7224,7 +7224,7 @@
         <v>98</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>78</v>
+        <v>351</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>78</v>
@@ -7233,7 +7233,7 @@
         <v>78</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>351</v>
+        <v>78</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>78</v>
@@ -7454,13 +7454,13 @@
         <v>78</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>78</v>
@@ -7571,13 +7571,13 @@
         <v>137</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM50" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>78</v>
@@ -7690,13 +7690,13 @@
         <v>137</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>78</v>
@@ -7923,13 +7923,13 @@
         <v>78</v>
       </c>
       <c r="AL53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>78</v>
@@ -8150,13 +8150,13 @@
         <v>78</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>78</v>
@@ -8267,13 +8267,13 @@
         <v>137</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>78</v>
@@ -8386,13 +8386,13 @@
         <v>137</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>78</v>
@@ -8619,13 +8619,13 @@
         <v>78</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>78</v>
@@ -8961,13 +8961,13 @@
         <v>78</v>
       </c>
       <c r="AK62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM62" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -9078,13 +9078,13 @@
         <v>137</v>
       </c>
       <c r="AK63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM63" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>78</v>
@@ -9197,13 +9197,13 @@
         <v>137</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM64" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>78</v>
@@ -9665,13 +9665,13 @@
         <v>401</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>78</v>
+        <v>402</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>403</v>
+        <v>78</v>
       </c>
     </row>
     <row r="69" hidden="true">
@@ -9774,16 +9774,16 @@
         <v>98</v>
       </c>
       <c r="AK69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM69" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="AL69" t="s" s="2">
+      <c r="AN69" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>78</v>
@@ -9891,16 +9891,16 @@
         <v>98</v>
       </c>
       <c r="AK70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM70" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="AL70" t="s" s="2">
+      <c r="AN70" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>78</v>
@@ -10008,16 +10008,16 @@
         <v>98</v>
       </c>
       <c r="AK71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM71" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="AL71" t="s" s="2">
+      <c r="AN71" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>78</v>
@@ -10125,16 +10125,16 @@
         <v>98</v>
       </c>
       <c r="AK72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM72" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AL72" t="s" s="2">
+      <c r="AN72" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>78</v>
@@ -10240,13 +10240,13 @@
         <v>98</v>
       </c>
       <c r="AK73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM73" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>78</v>
@@ -10355,13 +10355,13 @@
         <v>98</v>
       </c>
       <c r="AK74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM74" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>78</v>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2789" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2789" uniqueCount="444">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -741,6 +741,9 @@
   </si>
   <si>
     <t>The device identifier (DI) is a mandatory, fixed portion of a UDI that identifies the labeler and the specific version or model of a device.</t>
+  </si>
+  <si>
+    <t>1353: target not supported</t>
   </si>
   <si>
     <t>Role.id.extension</t>
@@ -883,6 +886,9 @@
     <t>http://hl7.org/fhir/ValueSet/device-status|4.0.1</t>
   </si>
   <si>
+    <t>1355: target not supported</t>
+  </si>
+  <si>
     <t>.statusCode</t>
   </si>
   <si>
@@ -920,6 +926,9 @@
     <t>For example, this applies to devices in the United States regulated under *Code of Federal Regulation 21CFR§1271.290(c)*.</t>
   </si>
   <si>
+    <t>1363: target not supported</t>
+  </si>
+  <si>
     <t>.lotNumberText</t>
   </si>
   <si>
@@ -957,6 +966,9 @@
     <t>The date and time when the device was manufactured.</t>
   </si>
   <si>
+    <t>1371: target not supported</t>
+  </si>
+  <si>
     <t>.existenceTime.low</t>
   </si>
   <si>
@@ -972,7 +984,7 @@
     <t>The date and time beyond which this device is no longer valid or should not be used (if applicable).</t>
   </si>
   <si>
-    <t>1373: source value from PROSTHESIS INSTALLED - STERILITY EXPIRATION DATE (#130.01-9)</t>
+    <t>1374: target not supported</t>
   </si>
   <si>
     <t>SPatient.ImplantedProsthesis.SterilityExpirationDate</t>
@@ -993,7 +1005,7 @@
     <t>Lot number assigned by the manufacturer.</t>
   </si>
   <si>
-    <t>1376: source value from PROSTHESIS INSTALLED - LOT NUMBER (#130.01-11)</t>
+    <t>1377: target not supported</t>
   </si>
   <si>
     <t>SPatient.ImplantedProsthesis.LotNumber</t>
@@ -1011,7 +1023,7 @@
     <t>Alphanumeric Maximum 20.</t>
   </si>
   <si>
-    <t>1379: source value from PROSTHESIS INSTALLED - SERIAL NUMBER (#130.01-12)</t>
+    <t>1381: target not supported</t>
   </si>
   <si>
     <t>SPatient.ImplantedProsthesis.SerialNumber</t>
@@ -1027,6 +1039,9 @@
   </si>
   <si>
     <t>This represents the manufacturer's name of the device as provided by the device, from a UDI label, or by a person describing the Device.  This typically would be used when a person provides the name(s) or when the device represents one of the names available from DeviceDefinition.</t>
+  </si>
+  <si>
+    <t>1386: target not supported</t>
   </si>
   <si>
     <t>Device.deviceName.id</t>
@@ -4672,31 +4687,31 @@
         <v>98</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>78</v>
+        <v>233</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4718,10 +4733,10 @@
         <v>100</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4772,7 +4787,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4793,21 +4808,21 @@
         <v>78</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4833,14 +4848,14 @@
         <v>100</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -4889,7 +4904,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4910,7 +4925,7 @@
         <v>78</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>78</v>
@@ -4921,14 +4936,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4947,16 +4962,16 @@
         <v>87</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5006,7 +5021,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5027,25 +5042,25 @@
         <v>78</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5067,13 +5082,13 @@
         <v>152</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5123,7 +5138,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5144,21 +5159,21 @@
         <v>78</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5184,14 +5199,14 @@
         <v>106</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>78</v>
@@ -5219,10 +5234,10 @@
         <v>168</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>78</v>
@@ -5240,7 +5255,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5261,7 +5276,7 @@
         <v>78</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>78</v>
@@ -5272,10 +5287,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5301,13 +5316,13 @@
         <v>106</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5336,10 +5351,10 @@
         <v>168</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>78</v>
@@ -5357,7 +5372,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5372,16 +5387,16 @@
         <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>78</v>
+        <v>274</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>78</v>
@@ -5389,10 +5404,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5418,10 +5433,10 @@
         <v>174</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5451,10 +5466,10 @@
         <v>179</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>78</v>
@@ -5472,7 +5487,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5496,7 +5511,7 @@
         <v>78</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>78</v>
@@ -5504,14 +5519,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5533,13 +5548,13 @@
         <v>152</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5589,7 +5604,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5604,27 +5619,27 @@
         <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>78</v>
+        <v>287</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5650,10 +5665,10 @@
         <v>152</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5704,7 +5719,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5719,16 +5734,16 @@
         <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>129</v>
@@ -5736,10 +5751,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5762,13 +5777,13 @@
         <v>78</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5819,7 +5834,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5834,27 +5849,27 @@
         <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>78</v>
+        <v>300</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5877,13 +5892,13 @@
         <v>78</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5934,7 +5949,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5949,27 +5964,27 @@
         <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5995,10 +6010,10 @@
         <v>152</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6049,7 +6064,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6064,27 +6079,27 @@
         <v>98</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6110,13 +6125,13 @@
         <v>152</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6166,7 +6181,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6181,16 +6196,16 @@
         <v>98</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>78</v>
@@ -6198,10 +6213,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6227,10 +6242,10 @@
         <v>217</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6281,7 +6296,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6296,7 +6311,7 @@
         <v>98</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>78</v>
+        <v>325</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>78</v>
@@ -6313,10 +6328,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6428,10 +6443,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6545,10 +6560,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6664,14 +6679,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6693,10 +6708,10 @@
         <v>152</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6747,7 +6762,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>86</v>
@@ -6762,10 +6777,10 @@
         <v>98</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>78</v>
@@ -6779,10 +6794,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6808,10 +6823,10 @@
         <v>106</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6841,10 +6856,10 @@
         <v>168</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>78</v>
@@ -6862,7 +6877,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>86</v>
@@ -6883,10 +6898,10 @@
         <v>78</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>78</v>
@@ -6894,10 +6909,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6923,10 +6938,10 @@
         <v>152</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6977,7 +6992,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6992,16 +7007,16 @@
         <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>78</v>
@@ -7009,10 +7024,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7038,13 +7053,13 @@
         <v>152</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7094,7 +7109,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7115,10 +7130,10 @@
         <v>78</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>78</v>
@@ -7126,10 +7141,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7155,10 +7170,10 @@
         <v>174</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7170,7 +7185,7 @@
         <v>78</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="T47" t="s" s="2">
         <v>78</v>
@@ -7188,28 +7203,28 @@
         <v>179</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Z47" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF47" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7224,7 +7239,7 @@
         <v>98</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>78</v>
@@ -7241,10 +7256,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7270,10 +7285,10 @@
         <v>217</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7324,7 +7339,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7356,10 +7371,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7471,10 +7486,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7588,10 +7603,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7707,14 +7722,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7736,10 +7751,10 @@
         <v>174</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7790,7 +7805,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>86</v>
@@ -7822,10 +7837,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7851,10 +7866,10 @@
         <v>152</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7905,7 +7920,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -7929,7 +7944,7 @@
         <v>78</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>78</v>
@@ -7937,10 +7952,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7966,10 +7981,10 @@
         <v>217</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8020,7 +8035,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8052,10 +8067,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8167,10 +8182,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8284,10 +8299,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8403,14 +8418,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8432,10 +8447,10 @@
         <v>174</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8486,7 +8501,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8518,10 +8533,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8547,10 +8562,10 @@
         <v>144</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8601,7 +8616,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8625,7 +8640,7 @@
         <v>78</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>78</v>
@@ -8633,10 +8648,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8662,10 +8677,10 @@
         <v>152</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8716,7 +8731,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>86</v>
@@ -8748,10 +8763,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8777,10 +8792,10 @@
         <v>217</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8831,7 +8846,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -8863,10 +8878,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8978,10 +8993,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9095,10 +9110,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9214,10 +9229,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9243,10 +9258,10 @@
         <v>174</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9297,7 +9312,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>86</v>
@@ -9329,10 +9344,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9355,13 +9370,13 @@
         <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9412,7 +9427,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9444,10 +9459,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9473,10 +9488,10 @@
         <v>174</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9527,7 +9542,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9559,10 +9574,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9585,17 +9600,17 @@
         <v>78</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>78</v>
@@ -9644,7 +9659,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9659,16 +9674,16 @@
         <v>98</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>78</v>
@@ -9676,10 +9691,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9705,10 +9720,10 @@
         <v>206</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9759,7 +9774,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9780,10 +9795,10 @@
         <v>78</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>78</v>
@@ -9791,10 +9806,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9817,16 +9832,16 @@
         <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9876,7 +9891,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -9897,10 +9912,10 @@
         <v>78</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>78</v>
@@ -9908,10 +9923,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9934,17 +9949,17 @@
         <v>78</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -9993,7 +10008,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10014,10 +10029,10 @@
         <v>78</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>78</v>
@@ -10025,10 +10040,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10054,13 +10069,13 @@
         <v>100</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10110,7 +10125,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10131,10 +10146,10 @@
         <v>78</v>
       </c>
       <c r="AM72" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AN72" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>78</v>
@@ -10142,10 +10157,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10168,13 +10183,13 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10225,7 +10240,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10246,7 +10261,7 @@
         <v>78</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>78</v>
@@ -10257,10 +10272,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10286,10 +10301,10 @@
         <v>174</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10340,7 +10355,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10361,7 +10376,7 @@
         <v>78</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>78</v>
@@ -10372,10 +10387,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10398,13 +10413,13 @@
         <v>78</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10455,7 +10470,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2789" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2789" uniqueCount="445">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -842,6 +842,9 @@
   </si>
   <si>
     <t>If separate barcodes for DI and PI are present, concatenate the string with DI first and in order of human readable expression on label.</t>
+  </si>
+  <si>
+    <t>1794: target not supported</t>
   </si>
   <si>
     <t>A unique device identifier (UDI) on a device label in plain text</t>
@@ -5153,7 +5156,7 @@
         <v>98</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>78</v>
+        <v>260</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>78</v>
@@ -5165,15 +5168,15 @@
         <v>78</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5199,14 +5202,14 @@
         <v>106</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>78</v>
@@ -5234,10 +5237,10 @@
         <v>168</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>78</v>
@@ -5255,7 +5258,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5276,7 +5279,7 @@
         <v>78</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>78</v>
@@ -5287,10 +5290,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5316,13 +5319,13 @@
         <v>106</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5351,10 +5354,10 @@
         <v>168</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>78</v>
@@ -5372,7 +5375,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5387,16 +5390,16 @@
         <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>78</v>
@@ -5404,10 +5407,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5433,10 +5436,10 @@
         <v>174</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5466,10 +5469,10 @@
         <v>179</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>78</v>
@@ -5487,7 +5490,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5511,7 +5514,7 @@
         <v>78</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>78</v>
@@ -5519,14 +5522,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5548,13 +5551,13 @@
         <v>152</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5604,7 +5607,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5619,27 +5622,27 @@
         <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>235</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5665,10 +5668,10 @@
         <v>152</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5719,7 +5722,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5734,13 +5737,13 @@
         <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>235</v>
@@ -5751,10 +5754,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5777,13 +5780,13 @@
         <v>78</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5834,7 +5837,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5849,27 +5852,27 @@
         <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>235</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5892,13 +5895,13 @@
         <v>78</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5949,7 +5952,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5964,27 +5967,27 @@
         <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>235</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6010,10 +6013,10 @@
         <v>152</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6064,7 +6067,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6079,27 +6082,27 @@
         <v>98</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>235</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6125,13 +6128,13 @@
         <v>152</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6181,7 +6184,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6196,13 +6199,13 @@
         <v>98</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>235</v>
@@ -6213,10 +6216,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6242,10 +6245,10 @@
         <v>217</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6296,7 +6299,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6311,7 +6314,7 @@
         <v>98</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>78</v>
@@ -6328,10 +6331,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6443,10 +6446,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6560,10 +6563,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6679,14 +6682,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6708,10 +6711,10 @@
         <v>152</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6762,7 +6765,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>86</v>
@@ -6777,10 +6780,10 @@
         <v>98</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>78</v>
@@ -6794,10 +6797,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6823,10 +6826,10 @@
         <v>106</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6856,10 +6859,10 @@
         <v>168</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>78</v>
@@ -6877,7 +6880,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>86</v>
@@ -6898,7 +6901,7 @@
         <v>78</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>235</v>
@@ -6909,10 +6912,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6938,10 +6941,10 @@
         <v>152</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6992,7 +6995,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7007,13 +7010,13 @@
         <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>235</v>
@@ -7024,10 +7027,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7053,13 +7056,13 @@
         <v>152</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7109,7 +7112,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7130,7 +7133,7 @@
         <v>78</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>235</v>
@@ -7141,10 +7144,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7170,10 +7173,10 @@
         <v>174</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7185,7 +7188,7 @@
         <v>78</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="T47" t="s" s="2">
         <v>78</v>
@@ -7203,10 +7206,10 @@
         <v>179</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>78</v>
@@ -7224,7 +7227,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7239,7 +7242,7 @@
         <v>98</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>78</v>
@@ -7256,10 +7259,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7285,10 +7288,10 @@
         <v>217</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7339,7 +7342,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7371,10 +7374,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7486,10 +7489,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7603,10 +7606,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7722,14 +7725,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7751,10 +7754,10 @@
         <v>174</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7805,7 +7808,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>86</v>
@@ -7837,10 +7840,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7866,10 +7869,10 @@
         <v>152</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7920,7 +7923,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -7952,10 +7955,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7981,10 +7984,10 @@
         <v>217</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8035,7 +8038,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8067,10 +8070,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8182,10 +8185,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8299,10 +8302,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8418,14 +8421,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8447,10 +8450,10 @@
         <v>174</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8501,7 +8504,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8533,10 +8536,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8562,10 +8565,10 @@
         <v>144</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8616,7 +8619,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8648,10 +8651,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8677,10 +8680,10 @@
         <v>152</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8731,7 +8734,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>86</v>
@@ -8763,10 +8766,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8792,10 +8795,10 @@
         <v>217</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8846,7 +8849,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -8878,10 +8881,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8993,10 +8996,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9110,10 +9113,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9229,10 +9232,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9258,10 +9261,10 @@
         <v>174</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9312,7 +9315,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>86</v>
@@ -9344,10 +9347,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9370,13 +9373,13 @@
         <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9427,7 +9430,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9459,10 +9462,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9488,10 +9491,10 @@
         <v>174</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9542,7 +9545,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9574,10 +9577,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9600,17 +9603,17 @@
         <v>78</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>78</v>
@@ -9659,7 +9662,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9674,16 +9677,16 @@
         <v>98</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>78</v>
@@ -9691,10 +9694,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9720,10 +9723,10 @@
         <v>206</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9774,7 +9777,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9795,10 +9798,10 @@
         <v>78</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>78</v>
@@ -9806,10 +9809,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9832,16 +9835,16 @@
         <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9891,7 +9894,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -9912,10 +9915,10 @@
         <v>78</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>78</v>
@@ -9923,10 +9926,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9949,17 +9952,17 @@
         <v>78</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -10008,7 +10011,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10029,10 +10032,10 @@
         <v>78</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>78</v>
@@ -10040,10 +10043,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10069,13 +10072,13 @@
         <v>100</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10125,7 +10128,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10146,10 +10149,10 @@
         <v>78</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>78</v>
@@ -10157,10 +10160,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10183,13 +10186,13 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10240,7 +10243,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10261,7 +10264,7 @@
         <v>78</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>78</v>
@@ -10272,10 +10275,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10301,10 +10304,10 @@
         <v>174</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10355,7 +10358,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10376,7 +10379,7 @@
         <v>78</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>78</v>
@@ -10387,10 +10390,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10413,13 +10416,13 @@
         <v>78</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10470,7 +10473,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -844,7 +844,7 @@
     <t>If separate barcodes for DI and PI are present, concatenate the string with DI first and in order of human readable expression on label.</t>
   </si>
   <si>
-    <t>1794: target not supported</t>
+    <t>1795: target not supported</t>
   </si>
   <si>
     <t>A unique device identifier (UDI) on a device label in plain text</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file PROSTHESIS INSTALLED (#130.01) to us-core-implantable-device</t>
+    <t>This StructureDefinition contains the maps for VistA file PROSTHESIS INSTALLED (130.01) to us-core-implantable-device</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -628,7 +628,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>1348: source value from PROSTHESIS INSTALLED - IEN (#130.01-.001)</t>
+    <t>1348: source value from PROSTHESIS INSTALLED - IEN (130.01-.001)</t>
   </si>
   <si>
     <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
@@ -947,7 +947,7 @@
     <t>A name of the manufacturer.</t>
   </si>
   <si>
-    <t>1365: source value from PROSTHESIS INSTALLED - VENDOR (#130.01-1)</t>
+    <t>1365: source value from PROSTHESIS INSTALLED - VENDOR (130.01-1)</t>
   </si>
   <si>
     <t>SPatient.ImplantedProsthesis.ProsthesisVendor</t>
@@ -1069,7 +1069,7 @@
     <t>The name of the device.</t>
   </si>
   <si>
-    <t>1385: source value from PROSTHESIS INSTALLED - PROSTHESIS ITEM &gt; PROSTHESIS - NAME (#130.01-.01 &gt; 131.9-.01)</t>
+    <t>1385: source value from PROSTHESIS INSTALLED - PROSTHESIS ITEM &gt; PROSTHESIS - NAME (130.01-.01 &gt; 131.9-.01)</t>
   </si>
   <si>
     <t>Dim.Prosthesis.ProsthesisName</t>
@@ -1103,7 +1103,7 @@
     <t>The model number for the device.</t>
   </si>
   <si>
-    <t>1387: source value from PROSTHESIS INSTALLED - MODEL (#130.01-2)</t>
+    <t>1387: source value from PROSTHESIS INSTALLED - MODEL (130.01-2)</t>
   </si>
   <si>
     <t>SPatient.ImplantedProsthesis.ProsthesisModel</t>
@@ -1294,7 +1294,7 @@
     <t>If the device is implanted in a patient, then need to associate the device to the patient.</t>
   </si>
   <si>
-    <t>1399: reference from SURGERY - PATIENT (#130-.01)</t>
+    <t>1399: reference from SURGERY - PATIENT (130-.01)</t>
   </si>
   <si>
     <t>Surg.AnesthesiaAgent.PatientIEN,Surg.AnesthesiaBlockSite.PatientIEN,Surg.AnesthesiaTechnique.PatientIEN,Surg.AnesthesiaTestDose.PatientIEN,Surg.ReferringPhysician.PatientIEN,Surg.ReplacementFluidType.PatientIEN,Surg.SurgeryAssistant.PatientIEN,Surg.SurgeryAssistantOther.PatientIEN,Surg.SurgeryDelay.PatientIEN,Surg.SurgeryINTRA.PatientIEN,Surg.SurgeryIrrigation.PatientIEN,Surg.SurgeryMedication.PatientIEN,Surg.SurgeryOccurrenceNonOp.PatientIEN,Surg.SurgeryOtherProcedure.PatientIEN,Surg.SurgeryOtherProcedureCPTModifier.PatientIEN,Surg.SurgeryOtherProcedureDiagnosis.PatientIEN,Surg.SurgeryPostOpDiagnosis.PatientIEN,Surg.SurgeryPreOpDiagnosis.PatientIEN,Surg.SurgeryPrincipalDiagnosis.PatientIEN,Surg.SurgeryProcedureCPTModifier.PatientIEN,Surg.SurgeryProcedureOccurrence.PatientIEN,Surg.SurgeryRequiredBloodProducts.PatientIEN,Surg.SurgeryReturnCase.PatientIEN,Surg.SurgORCircSupport.PatientIEN,Surg.SurgORCircSupportTime.PatientIEN,Surg.SurgORScrubSupport.PatientIEN,Surg.SurgORScrubSupportTime.PatientIEN</t>
@@ -1767,7 +1767,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="111.0546875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="109.51953125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="102.6171875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2789" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2789" uniqueCount="447">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1072,7 +1072,8 @@
     <t>1385: source value from PROSTHESIS INSTALLED - PROSTHESIS ITEM &gt; PROSTHESIS - NAME (130.01-.01 &gt; 131.9-.01)</t>
   </si>
   <si>
-    <t>Dim.Prosthesis.ProsthesisName</t>
+    <t>SPatient.ImplantedProsthesis.ProsthesisIEN
+Dim.Prosthesis.ProsthesisName</t>
   </si>
   <si>
     <t>Device.deviceName.type</t>
@@ -1297,7 +1298,7 @@
     <t>1399: reference from SURGERY - PATIENT (130-.01)</t>
   </si>
   <si>
-    <t>Surg.AnesthesiaAgent.PatientIEN,Surg.AnesthesiaBlockSite.PatientIEN,Surg.AnesthesiaTechnique.PatientIEN,Surg.AnesthesiaTestDose.PatientIEN,Surg.ReferringPhysician.PatientIEN,Surg.ReplacementFluidType.PatientIEN,Surg.SurgeryAssistant.PatientIEN,Surg.SurgeryAssistantOther.PatientIEN,Surg.SurgeryDelay.PatientIEN,Surg.SurgeryINTRA.PatientIEN,Surg.SurgeryIrrigation.PatientIEN,Surg.SurgeryMedication.PatientIEN,Surg.SurgeryOccurrenceNonOp.PatientIEN,Surg.SurgeryOtherProcedure.PatientIEN,Surg.SurgeryOtherProcedureCPTModifier.PatientIEN,Surg.SurgeryOtherProcedureDiagnosis.PatientIEN,Surg.SurgeryPostOpDiagnosis.PatientIEN,Surg.SurgeryPreOpDiagnosis.PatientIEN,Surg.SurgeryPrincipalDiagnosis.PatientIEN,Surg.SurgeryProcedureCPTModifier.PatientIEN,Surg.SurgeryProcedureOccurrence.PatientIEN,Surg.SurgeryRequiredBloodProducts.PatientIEN,Surg.SurgeryReturnCase.PatientIEN,Surg.SurgORCircSupport.PatientIEN,Surg.SurgORCircSupportTime.PatientIEN,Surg.SurgORScrubSupport.PatientIEN,Surg.SurgORScrubSupportTime.PatientIEN</t>
+    <t>SPatient.ImplantedProsthesis.PatientIEN,SPatient.OperationsIndication.PatientIEN,Surg.AnesthesiaAgent.PatientIEN,Surg.AnesthesiaBlockSite.PatientIEN,Surg.AnesthesiaTechnique.PatientIEN,Surg.AnesthesiaTestDose.PatientIEN,Surg.ReferringPhysician.PatientIEN,Surg.ReferringPhysician.PatientSID,Surg.ReplacementFluidType.PatientIEN,Surg.ReplacementFluidType.PatientSID,Surg.SurgeryAssistant.PatientIEN,Surg.SurgeryAssistantOther.PatientIEN,Surg.SurgeryDelay.PatientIEN,Surg.SurgeryINTRA.PatientIEN,Surg.SurgeryIrrigation.PatientIEN,Surg.SurgeryIrrigation.PatientSID,Surg.SurgeryMedication.PatientIEN,Surg.SurgeryOccurrenceNonOp.PatientIEN,Surg.SurgeryOccurrenceNonOp.PatientSID,Surg.SurgeryOtherPostOpDiagnosis.PatientIEN,Surg.SurgeryOtherProcedure.PatientIEN,Surg.SurgeryOtherProcedureCPTModifier.PatientIEN,Surg.SurgeryOtherProcedureCPTModifier.PatientSID,Surg.SurgeryOtherProcedureDiagnosis.PatientIEN,Surg.SurgeryPOST.PatientIEN,Surg.SurgeryPostOpDiagnosis.PatientIEN,Surg.SurgeryPreOpDiagnosis.PatientIEN,Surg.SurgeryPreOpDiagnosis.PatientSID,Surg.SurgeryPrincipalAssociatedDiagnosis.PatientIEN,Surg.SurgeryPrincipalAssociatedProcedure.PatientIEN,Surg.SurgeryPrincipalCPTModifier.PatientIEN,Surg.SurgeryPrincipalDiagnosis.PatientIEN,Surg.SurgeryProcedureCPTModifier.PatientIEN,Surg.SurgeryProcedureDiagnosisCode.PatientIEN,Surg.SurgeryProcedureOccurrence.PatientIEN,Surg.SurgeryProcedureOccurrence.PatientSID,Surg.SurgeryRequiredBloodProducts.PatientIEN,Surg.SurgeryReturnCase.PatientIEN,Surg.SurgORCircSupport.PatientIEN,Surg.SurgORCircSupportTime.PatientIEN,Surg.SurgORCircSupportTime.PatientSID,Surg.SurgORScrubSupport.PatientIEN,Surg.SurgORScrubSupportTime.PatientIEN,Surg.SurgORScrubSupportTime.PatientSID</t>
   </si>
   <si>
     <t>.playedRole[typeCode=USED].scoper.playedRole[typeCode=PAT]</t>
@@ -1313,6 +1314,12 @@
   </si>
   <si>
     <t>An organization that is responsible for the provision and ongoing maintenance of the device.</t>
+  </si>
+  <si>
+    <t>1807: reference from SURGERY - DIVISION (130-50)</t>
+  </si>
+  <si>
+    <t>Surg.SurgeryINTRA.InstitutionIEN,Surg.SurgeryPOST.InstitutionIEN</t>
   </si>
   <si>
     <t>.playedRole[typeCode=OWN].scoper</t>
@@ -9711,7 +9718,7 @@
         <v>86</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>78</v>
@@ -9792,16 +9799,16 @@
         <v>98</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>78</v>
+        <v>413</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>78</v>
+        <v>414</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>78</v>
@@ -9809,10 +9816,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9835,16 +9842,16 @@
         <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9894,7 +9901,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -9915,10 +9922,10 @@
         <v>78</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>78</v>
@@ -9926,10 +9933,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9952,17 +9959,17 @@
         <v>78</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -10011,7 +10018,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10032,10 +10039,10 @@
         <v>78</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>78</v>
@@ -10043,10 +10050,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10072,13 +10079,13 @@
         <v>100</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10128,7 +10135,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10149,10 +10156,10 @@
         <v>78</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>78</v>
@@ -10160,10 +10167,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10186,13 +10193,13 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10243,7 +10250,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10264,7 +10271,7 @@
         <v>78</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>78</v>
@@ -10275,10 +10282,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10304,10 +10311,10 @@
         <v>174</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10358,7 +10365,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10390,10 +10397,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10416,13 +10423,13 @@
         <v>78</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10473,7 +10480,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2789" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2789" uniqueCount="451">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -601,10 +601,16 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
+    <t>http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+  </si>
+  <si>
     <t>http://www.acme.com/identifiers/patient</t>
   </si>
   <si>
     <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>1348-1: fixed value = http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
   </si>
   <si>
     <t>II.root or Role.id.root</t>
@@ -1086,10 +1092,16 @@
 UDILabelName | UserFriendlyName | PatientReportedName | ManufactureDeviceName | ModelName.</t>
   </si>
   <si>
+    <t>model-name</t>
+  </si>
+  <si>
     <t>The type of name the device is referred by.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/device-nametype|4.0.1</t>
+  </si>
+  <si>
+    <t>1385-1: fixed value = #model-name</t>
   </si>
   <si>
     <t>.playedRole[typeCode=MANU].code</t>
@@ -3565,7 +3577,7 @@
         <v>86</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>78</v>
@@ -3596,10 +3608,10 @@
         <v>78</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>78</v>
+        <v>188</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>78</v>
@@ -3635,7 +3647,7 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3650,13 +3662,13 @@
         <v>98</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>78</v>
+        <v>191</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>78</v>
@@ -3667,10 +3679,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3696,13 +3708,13 @@
         <v>152</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3716,7 +3728,7 @@
         <v>78</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>78</v>
@@ -3752,7 +3764,7 @@
         <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3767,13 +3779,13 @@
         <v>98</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>78</v>
@@ -3784,10 +3796,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3810,13 +3822,13 @@
         <v>87</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3867,7 +3879,7 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3888,7 +3900,7 @@
         <v>78</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>78</v>
@@ -3899,10 +3911,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3925,16 +3937,16 @@
         <v>87</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3984,7 +3996,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4005,7 +4017,7 @@
         <v>78</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>78</v>
@@ -4016,10 +4028,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4042,13 +4054,13 @@
         <v>78</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4099,7 +4111,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -4131,10 +4143,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4157,16 +4169,16 @@
         <v>87</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4216,7 +4228,7 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4237,7 +4249,7 @@
         <v>78</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>149</v>
@@ -4248,10 +4260,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4363,10 +4375,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4480,14 +4492,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4509,10 +4521,10 @@
         <v>132</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N24" t="s" s="2">
         <v>135</v>
@@ -4567,7 +4579,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4599,14 +4611,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4628,10 +4640,10 @@
         <v>152</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4682,7 +4694,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4697,31 +4709,31 @@
         <v>98</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4743,10 +4755,10 @@
         <v>100</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4797,7 +4809,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4818,21 +4830,21 @@
         <v>78</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4858,14 +4870,14 @@
         <v>100</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -4914,7 +4926,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4935,7 +4947,7 @@
         <v>78</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>78</v>
@@ -4946,14 +4958,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4972,16 +4984,16 @@
         <v>87</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5031,7 +5043,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5052,25 +5064,25 @@
         <v>78</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5092,13 +5104,13 @@
         <v>152</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5148,7 +5160,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5163,27 +5175,27 @@
         <v>98</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5209,14 +5221,14 @@
         <v>106</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>78</v>
@@ -5244,10 +5256,10 @@
         <v>168</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>78</v>
@@ -5265,7 +5277,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5286,7 +5298,7 @@
         <v>78</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>78</v>
@@ -5297,10 +5309,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5326,13 +5338,13 @@
         <v>106</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5361,10 +5373,10 @@
         <v>168</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>78</v>
@@ -5382,7 +5394,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5397,16 +5409,16 @@
         <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>78</v>
@@ -5414,10 +5426,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5443,10 +5455,10 @@
         <v>174</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5476,10 +5488,10 @@
         <v>179</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>78</v>
@@ -5497,7 +5509,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5521,7 +5533,7 @@
         <v>78</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>78</v>
@@ -5529,14 +5541,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5558,13 +5570,13 @@
         <v>152</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5614,7 +5626,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5629,27 +5641,27 @@
         <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5675,10 +5687,10 @@
         <v>152</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5729,7 +5741,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5744,16 +5756,16 @@
         <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>129</v>
@@ -5761,10 +5773,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5787,13 +5799,13 @@
         <v>78</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5844,7 +5856,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5859,27 +5871,27 @@
         <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5902,13 +5914,13 @@
         <v>78</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5959,7 +5971,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5974,27 +5986,27 @@
         <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6020,10 +6032,10 @@
         <v>152</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6074,7 +6086,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6089,27 +6101,27 @@
         <v>98</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6135,13 +6147,13 @@
         <v>152</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6191,7 +6203,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6206,16 +6218,16 @@
         <v>98</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>78</v>
@@ -6223,10 +6235,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6249,13 +6261,13 @@
         <v>78</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6306,7 +6318,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6321,7 +6333,7 @@
         <v>98</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>78</v>
@@ -6338,10 +6350,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6453,10 +6465,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6570,14 +6582,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6599,10 +6611,10 @@
         <v>132</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>135</v>
@@ -6657,7 +6669,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6689,14 +6701,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6718,10 +6730,10 @@
         <v>152</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6772,7 +6784,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>86</v>
@@ -6787,10 +6799,10 @@
         <v>98</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>78</v>
@@ -6804,10 +6816,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6821,7 +6833,7 @@
         <v>86</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>78</v>
@@ -6833,10 +6845,10 @@
         <v>106</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6848,7 +6860,7 @@
         <v>78</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>78</v>
+        <v>341</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>78</v>
@@ -6866,10 +6878,10 @@
         <v>168</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>78</v>
@@ -6887,7 +6899,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>86</v>
@@ -6902,16 +6914,16 @@
         <v>98</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>78</v>
+        <v>344</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>78</v>
@@ -6919,10 +6931,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6948,10 +6960,10 @@
         <v>152</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7002,7 +7014,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7017,16 +7029,16 @@
         <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>78</v>
@@ -7034,10 +7046,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7063,13 +7075,13 @@
         <v>152</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7119,7 +7131,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7140,10 +7152,10 @@
         <v>78</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>78</v>
@@ -7151,10 +7163,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7180,10 +7192,10 @@
         <v>174</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7195,7 +7207,7 @@
         <v>78</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="T47" t="s" s="2">
         <v>78</v>
@@ -7213,28 +7225,28 @@
         <v>179</v>
       </c>
       <c r="Y47" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF47" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7249,7 +7261,7 @@
         <v>98</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>78</v>
@@ -7266,10 +7278,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7292,13 +7304,13 @@
         <v>78</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7349,7 +7361,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7381,10 +7393,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7496,10 +7508,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7613,14 +7625,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7642,10 +7654,10 @@
         <v>132</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>135</v>
@@ -7700,7 +7712,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7732,14 +7744,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7761,10 +7773,10 @@
         <v>174</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7815,7 +7827,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>86</v>
@@ -7847,10 +7859,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7876,10 +7888,10 @@
         <v>152</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7930,7 +7942,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -7954,7 +7966,7 @@
         <v>78</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>78</v>
@@ -7962,10 +7974,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7988,13 +8000,13 @@
         <v>78</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8045,7 +8057,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8077,10 +8089,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8192,10 +8204,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8309,14 +8321,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8338,10 +8350,10 @@
         <v>132</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>135</v>
@@ -8396,7 +8408,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8428,14 +8440,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8457,10 +8469,10 @@
         <v>174</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8511,7 +8523,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8543,10 +8555,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8572,10 +8584,10 @@
         <v>144</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8626,7 +8638,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8650,7 +8662,7 @@
         <v>78</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>78</v>
@@ -8658,10 +8670,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8687,10 +8699,10 @@
         <v>152</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8741,7 +8753,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>86</v>
@@ -8773,10 +8785,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8799,13 +8811,13 @@
         <v>78</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8856,7 +8868,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -8888,10 +8900,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9003,10 +9015,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9120,14 +9132,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9149,10 +9161,10 @@
         <v>132</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>135</v>
@@ -9207,7 +9219,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9239,10 +9251,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9268,10 +9280,10 @@
         <v>174</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9322,7 +9334,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>86</v>
@@ -9354,10 +9366,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9380,13 +9392,13 @@
         <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9437,7 +9449,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9469,10 +9481,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9498,10 +9510,10 @@
         <v>174</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9552,7 +9564,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9584,10 +9596,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9610,17 +9622,17 @@
         <v>78</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>78</v>
@@ -9669,7 +9681,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9684,16 +9696,16 @@
         <v>98</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>78</v>
@@ -9701,10 +9713,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9727,13 +9739,13 @@
         <v>78</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9784,7 +9796,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9799,16 +9811,16 @@
         <v>98</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>78</v>
@@ -9816,10 +9828,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9842,16 +9854,16 @@
         <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9901,7 +9913,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -9922,10 +9934,10 @@
         <v>78</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>78</v>
@@ -9933,10 +9945,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9959,17 +9971,17 @@
         <v>78</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -10018,7 +10030,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10039,10 +10051,10 @@
         <v>78</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>78</v>
@@ -10050,10 +10062,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10079,13 +10091,13 @@
         <v>100</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10135,7 +10147,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10156,10 +10168,10 @@
         <v>78</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>78</v>
@@ -10167,10 +10179,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10193,13 +10205,13 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10250,7 +10262,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10271,7 +10283,7 @@
         <v>78</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>78</v>
@@ -10282,10 +10294,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10311,10 +10323,10 @@
         <v>174</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10365,7 +10377,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10386,7 +10398,7 @@
         <v>78</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>78</v>
@@ -10397,10 +10409,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10423,13 +10435,13 @@
         <v>78</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10480,7 +10492,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -601,7 +601,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+    <t>http://va.gov/fhir/identifiers/Sta3n$stationNr/130.01</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -610,7 +610,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>1348-1: fixed value = http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+    <t>1348-1: fixed value = http://va.gov/fhir/identifiers/Sta3n$stationNr/130.01</t>
   </si>
   <si>
     <t>II.root or Role.id.root</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -601,7 +601,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identifiers/Sta3n$stationNr/130.01</t>
+    <t>http://va.gov/identifiers/$Sta3n/130.01</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -610,7 +610,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>1348-1: fixed value = http://va.gov/fhir/identifiers/Sta3n$stationNr/130.01</t>
+    <t>1348-1: fixed value = http://va.gov/identifiers/$Sta3n/130.01</t>
   </si>
   <si>
     <t>II.root or Role.id.root</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2789" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2789" uniqueCount="447">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-21T15:05:18+00:00</t>
+    <t>2024-07-09T16:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -601,7 +601,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/identifiers/$Sta3n/130.01</t>
+    <t>http://va.gov/identifiers/$Sta3n/131.01</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -610,7 +610,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>1348-1: fixed value = http://va.gov/identifiers/$Sta3n/130.01</t>
+    <t>1348-1: fixed value = http://va.gov/identifiers/$Sta3n/131.01</t>
   </si>
   <si>
     <t>II.root or Role.id.root</t>
@@ -1075,13 +1075,6 @@
     <t>The name of the device.</t>
   </si>
   <si>
-    <t>1385: source value from PROSTHESIS INSTALLED - PROSTHESIS ITEM &gt; PROSTHESIS - NAME (130.01-.01 &gt; 131.9-.01)</t>
-  </si>
-  <si>
-    <t>SPatient.ImplantedProsthesis.ProsthesisIEN
-Dim.Prosthesis.ProsthesisName</t>
-  </si>
-  <si>
     <t>Device.deviceName.type</t>
   </si>
   <si>
@@ -1092,16 +1085,10 @@
 UDILabelName | UserFriendlyName | PatientReportedName | ManufactureDeviceName | ModelName.</t>
   </si>
   <si>
-    <t>model-name</t>
-  </si>
-  <si>
     <t>The type of name the device is referred by.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/device-nametype|4.0.1</t>
-  </si>
-  <si>
-    <t>1385-1: fixed value = #model-name</t>
   </si>
   <si>
     <t>.playedRole[typeCode=MANU].code</t>
@@ -1786,7 +1773,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="109.51953125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="102.6171875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
@@ -6718,7 +6705,7 @@
         <v>86</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>78</v>
@@ -6799,10 +6786,10 @@
         <v>98</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>336</v>
+        <v>78</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>337</v>
+        <v>78</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>78</v>
@@ -6816,10 +6803,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6833,7 +6820,7 @@
         <v>86</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>78</v>
@@ -6845,10 +6832,10 @@
         <v>106</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6860,7 +6847,7 @@
         <v>78</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>341</v>
+        <v>78</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>78</v>
@@ -6878,10 +6865,10 @@
         <v>168</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>78</v>
@@ -6899,7 +6886,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>86</v>
@@ -6914,13 +6901,13 @@
         <v>98</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>344</v>
+        <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>237</v>
@@ -6931,10 +6918,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6960,10 +6947,10 @@
         <v>152</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7014,7 +7001,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7029,13 +7016,13 @@
         <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>237</v>
@@ -7046,10 +7033,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7075,10 +7062,10 @@
         <v>152</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>321</v>
@@ -7131,7 +7118,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7163,10 +7150,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7192,10 +7179,10 @@
         <v>174</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7207,7 +7194,7 @@
         <v>78</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="T47" t="s" s="2">
         <v>78</v>
@@ -7225,10 +7212,10 @@
         <v>179</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>78</v>
@@ -7246,7 +7233,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7261,7 +7248,7 @@
         <v>98</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>78</v>
@@ -7278,10 +7265,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7307,10 +7294,10 @@
         <v>219</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7361,7 +7348,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7393,10 +7380,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7508,10 +7495,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7625,10 +7612,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7744,10 +7731,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7773,10 +7760,10 @@
         <v>174</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7827,7 +7814,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>86</v>
@@ -7859,10 +7846,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7888,10 +7875,10 @@
         <v>152</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7942,7 +7929,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -7974,10 +7961,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8003,10 +7990,10 @@
         <v>219</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8057,7 +8044,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8089,10 +8076,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8204,10 +8191,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8321,10 +8308,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8440,10 +8427,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8469,10 +8456,10 @@
         <v>174</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8523,7 +8510,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8555,10 +8542,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8584,10 +8571,10 @@
         <v>144</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8638,7 +8625,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8670,10 +8657,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8699,10 +8686,10 @@
         <v>152</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8753,7 +8740,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>86</v>
@@ -8785,10 +8772,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8814,10 +8801,10 @@
         <v>219</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8868,7 +8855,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -8900,10 +8887,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9015,10 +9002,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9132,10 +9119,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9251,10 +9238,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9280,10 +9267,10 @@
         <v>174</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9334,7 +9321,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>86</v>
@@ -9366,10 +9353,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9392,13 +9379,13 @@
         <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9449,7 +9436,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9481,10 +9468,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9510,10 +9497,10 @@
         <v>174</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9564,7 +9551,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9596,10 +9583,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9622,17 +9609,17 @@
         <v>78</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>78</v>
@@ -9681,7 +9668,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9696,16 +9683,16 @@
         <v>98</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>78</v>
@@ -9713,10 +9700,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9742,10 +9729,10 @@
         <v>208</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9796,7 +9783,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9811,16 +9798,16 @@
         <v>98</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>78</v>
@@ -9828,10 +9815,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9854,16 +9841,16 @@
         <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9913,7 +9900,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -9934,10 +9921,10 @@
         <v>78</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>78</v>
@@ -9945,10 +9932,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9971,17 +9958,17 @@
         <v>78</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -10030,7 +10017,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10051,10 +10038,10 @@
         <v>78</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>78</v>
@@ -10062,10 +10049,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10091,13 +10078,13 @@
         <v>100</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10147,7 +10134,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10168,10 +10155,10 @@
         <v>78</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>78</v>
@@ -10179,10 +10166,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10205,13 +10192,13 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10262,7 +10249,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10283,7 +10270,7 @@
         <v>78</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>78</v>
@@ -10294,10 +10281,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10323,10 +10310,10 @@
         <v>174</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10377,7 +10364,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10409,10 +10396,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10435,13 +10422,13 @@
         <v>78</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10492,7 +10479,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2789" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2789" uniqueCount="451">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1075,6 +1075,13 @@
     <t>The name of the device.</t>
   </si>
   <si>
+    <t>1385: source value from PROSTHESIS INSTALLED - PROSTHESIS ITEM &gt; PROSTHESIS - NAME (130.01-.01 &gt; 131.9-.01)</t>
+  </si>
+  <si>
+    <t>SPatient.ImplantedProsthesis.ProsthesisIEN
+Dim.Prosthesis.ProsthesisName</t>
+  </si>
+  <si>
     <t>Device.deviceName.type</t>
   </si>
   <si>
@@ -1085,10 +1092,16 @@
 UDILabelName | UserFriendlyName | PatientReportedName | ManufactureDeviceName | ModelName.</t>
   </si>
   <si>
+    <t>model-name</t>
+  </si>
+  <si>
     <t>The type of name the device is referred by.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/device-nametype|4.0.1</t>
+  </si>
+  <si>
+    <t>1385-1: fixed value = #model-name</t>
   </si>
   <si>
     <t>.playedRole[typeCode=MANU].code</t>
@@ -1773,7 +1786,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="109.51953125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="102.6171875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
@@ -6705,7 +6718,7 @@
         <v>86</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>78</v>
@@ -6786,10 +6799,10 @@
         <v>98</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>78</v>
+        <v>336</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>78</v>
+        <v>337</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>78</v>
@@ -6803,10 +6816,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6820,7 +6833,7 @@
         <v>86</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>78</v>
@@ -6832,10 +6845,10 @@
         <v>106</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6847,7 +6860,7 @@
         <v>78</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>78</v>
+        <v>341</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>78</v>
@@ -6865,10 +6878,10 @@
         <v>168</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>78</v>
@@ -6886,7 +6899,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>86</v>
@@ -6901,13 +6914,13 @@
         <v>98</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>78</v>
+        <v>344</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>237</v>
@@ -6918,10 +6931,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6947,10 +6960,10 @@
         <v>152</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7001,7 +7014,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7016,13 +7029,13 @@
         <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>237</v>
@@ -7033,10 +7046,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7062,10 +7075,10 @@
         <v>152</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>321</v>
@@ -7118,7 +7131,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7150,10 +7163,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7179,10 +7192,10 @@
         <v>174</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7194,7 +7207,7 @@
         <v>78</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="T47" t="s" s="2">
         <v>78</v>
@@ -7212,28 +7225,28 @@
         <v>179</v>
       </c>
       <c r="Y47" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF47" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7248,7 +7261,7 @@
         <v>98</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>78</v>
@@ -7265,10 +7278,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7294,10 +7307,10 @@
         <v>219</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7348,7 +7361,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7380,10 +7393,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7495,10 +7508,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7612,10 +7625,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7731,10 +7744,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7760,10 +7773,10 @@
         <v>174</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7814,7 +7827,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>86</v>
@@ -7846,10 +7859,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7875,10 +7888,10 @@
         <v>152</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7929,7 +7942,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -7961,10 +7974,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7990,10 +8003,10 @@
         <v>219</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8044,7 +8057,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8076,10 +8089,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8191,10 +8204,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8308,10 +8321,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8427,10 +8440,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8456,10 +8469,10 @@
         <v>174</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8510,7 +8523,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8542,10 +8555,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8571,10 +8584,10 @@
         <v>144</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8625,7 +8638,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8657,10 +8670,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8686,10 +8699,10 @@
         <v>152</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8740,7 +8753,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>86</v>
@@ -8772,10 +8785,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8801,10 +8814,10 @@
         <v>219</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8855,7 +8868,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -8887,10 +8900,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9002,10 +9015,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9119,10 +9132,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9238,10 +9251,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9267,10 +9280,10 @@
         <v>174</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9321,7 +9334,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>86</v>
@@ -9353,10 +9366,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9379,13 +9392,13 @@
         <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9436,7 +9449,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9468,10 +9481,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9497,10 +9510,10 @@
         <v>174</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9551,7 +9564,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9583,10 +9596,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9609,17 +9622,17 @@
         <v>78</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>78</v>
@@ -9668,7 +9681,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9683,16 +9696,16 @@
         <v>98</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>78</v>
@@ -9700,10 +9713,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9729,10 +9742,10 @@
         <v>208</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9783,7 +9796,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9798,16 +9811,16 @@
         <v>98</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>78</v>
@@ -9815,10 +9828,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9841,16 +9854,16 @@
         <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9900,7 +9913,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -9921,10 +9934,10 @@
         <v>78</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>78</v>
@@ -9932,10 +9945,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9958,17 +9971,17 @@
         <v>78</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -10017,7 +10030,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10038,10 +10051,10 @@
         <v>78</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>78</v>
@@ -10049,10 +10062,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10078,13 +10091,13 @@
         <v>100</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10134,7 +10147,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10155,10 +10168,10 @@
         <v>78</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>78</v>
@@ -10166,10 +10179,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10192,13 +10205,13 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10249,7 +10262,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10270,7 +10283,7 @@
         <v>78</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>78</v>
@@ -10281,10 +10294,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10310,10 +10323,10 @@
         <v>174</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10364,7 +10377,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10396,10 +10409,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10422,13 +10435,13 @@
         <v>78</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10479,7 +10492,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1294,7 +1294,7 @@
     <t>Device.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>
@@ -1761,7 +1761,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="67.61328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="52.44140625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1158,7 +1158,7 @@
     <t>http://hl7.org/fhir/ValueSet/device-kind</t>
   </si>
   <si>
-    <t>1393: fixed value = http://snomed.info/sct#63653004 Biomedical device</t>
+    <t>1393: fixed value = http://snomed.info/sct#63653004 "Biomedical device"</t>
   </si>
   <si>
     <t>Device.specialization</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -243,7 +243,7 @@
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
-    <t>Mapping: Virtual Patient Record (VPR)</t>
+    <t>Mapping: Summary Document Architecure (SDA)</t>
   </si>
   <si>
     <t>Mapping: RIM Mapping</t>
@@ -1798,7 +1798,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="109.51953125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="51.63671875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="102.6171875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2864" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2864" uniqueCount="455">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1316,6 +1316,9 @@
     <t>SPatient.ImplantedProsthesis.PatientIEN,SPatient.OperationsIndication.PatientIEN,Surg.AnesthesiaAgent.PatientIEN,Surg.AnesthesiaBlockSite.PatientIEN,Surg.AnesthesiaTechnique.PatientIEN,Surg.AnesthesiaTestDose.PatientIEN,Surg.ReferringPhysician.PatientIEN,Surg.ReferringPhysician.PatientSID,Surg.ReplacementFluidType.PatientIEN,Surg.ReplacementFluidType.PatientSID,Surg.SurgeryAssistant.PatientIEN,Surg.SurgeryAssistantOther.PatientIEN,Surg.SurgeryDelay.PatientIEN,Surg.SurgeryINTRA.PatientIEN,Surg.SurgeryIrrigation.PatientIEN,Surg.SurgeryIrrigation.PatientSID,Surg.SurgeryMedication.PatientIEN,Surg.SurgeryOccurrenceNonOp.PatientIEN,Surg.SurgeryOccurrenceNonOp.PatientSID,Surg.SurgeryOtherPostOpDiagnosis.PatientIEN,Surg.SurgeryOtherProcedure.PatientIEN,Surg.SurgeryOtherProcedureCPTModifier.PatientIEN,Surg.SurgeryOtherProcedureCPTModifier.PatientSID,Surg.SurgeryOtherProcedureDiagnosis.PatientIEN,Surg.SurgeryPOST.PatientIEN,Surg.SurgeryPostOpDiagnosis.PatientIEN,Surg.SurgeryPreOpDiagnosis.PatientIEN,Surg.SurgeryPreOpDiagnosis.PatientSID,Surg.SurgeryPrincipalAssociatedDiagnosis.PatientIEN,Surg.SurgeryPrincipalAssociatedProcedure.PatientIEN,Surg.SurgeryPrincipalCPTModifier.PatientIEN,Surg.SurgeryPrincipalDiagnosis.PatientIEN,Surg.SurgeryProcedureCPTModifier.PatientIEN,Surg.SurgeryProcedureDiagnosisCode.PatientIEN,Surg.SurgeryProcedureOccurrence.PatientIEN,Surg.SurgeryProcedureOccurrence.PatientSID,Surg.SurgeryRequiredBloodProducts.PatientIEN,Surg.SurgeryReturnCase.PatientIEN,Surg.SurgORCircSupport.PatientIEN,Surg.SurgORCircSupportTime.PatientIEN,Surg.SurgORCircSupportTime.PatientSID,Surg.SurgORScrubSupport.PatientIEN,Surg.SurgORScrubSupportTime.PatientIEN,Surg.SurgORScrubSupportTime.PatientSID</t>
   </si>
   <si>
+    <t>Procedure.CodeTableDetail.Procedure.Code</t>
+  </si>
+  <si>
     <t>.playedRole[typeCode=USED].scoper.playedRole[typeCode=PAT]</t>
   </si>
   <si>
@@ -1341,7 +1344,7 @@
     <t>Surg.SurgeryINTRA.InstitutionIEN,Surg.SurgeryPOST.InstitutionIEN</t>
   </si>
   <si>
-    <t>surgery.facility</t>
+    <t>Procedure.EnteredAt</t>
   </si>
   <si>
     <t>.playedRole[typeCode=OWN].scoper</t>
@@ -9914,13 +9917,13 @@
         <v>412</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>79</v>
+        <v>413</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>79</v>
@@ -9928,10 +9931,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9954,13 +9957,13 @@
         <v>79</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10011,7 +10014,7 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10026,19 +10029,19 @@
         <v>99</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>79</v>
@@ -10046,10 +10049,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10072,16 +10075,16 @@
         <v>79</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10131,7 +10134,7 @@
         <v>79</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10155,10 +10158,10 @@
         <v>79</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>79</v>
@@ -10166,10 +10169,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10192,17 +10195,17 @@
         <v>79</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>79</v>
@@ -10251,7 +10254,7 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10275,10 +10278,10 @@
         <v>79</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>79</v>
@@ -10286,10 +10289,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10315,13 +10318,13 @@
         <v>101</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10371,7 +10374,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10395,10 +10398,10 @@
         <v>79</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>79</v>
@@ -10406,10 +10409,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10432,13 +10435,13 @@
         <v>79</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10489,7 +10492,7 @@
         <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10513,7 +10516,7 @@
         <v>79</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>79</v>
@@ -10524,10 +10527,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10553,10 +10556,10 @@
         <v>175</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10607,7 +10610,7 @@
         <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -10642,10 +10645,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10668,13 +10671,13 @@
         <v>79</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10725,7 +10728,7 @@
         <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1316,7 +1316,7 @@
     <t>SPatient.ImplantedProsthesis.PatientIEN,SPatient.OperationsIndication.PatientIEN,Surg.AnesthesiaAgent.PatientIEN,Surg.AnesthesiaBlockSite.PatientIEN,Surg.AnesthesiaTechnique.PatientIEN,Surg.AnesthesiaTestDose.PatientIEN,Surg.ReferringPhysician.PatientIEN,Surg.ReferringPhysician.PatientSID,Surg.ReplacementFluidType.PatientIEN,Surg.ReplacementFluidType.PatientSID,Surg.SurgeryAssistant.PatientIEN,Surg.SurgeryAssistantOther.PatientIEN,Surg.SurgeryDelay.PatientIEN,Surg.SurgeryINTRA.PatientIEN,Surg.SurgeryIrrigation.PatientIEN,Surg.SurgeryIrrigation.PatientSID,Surg.SurgeryMedication.PatientIEN,Surg.SurgeryOccurrenceNonOp.PatientIEN,Surg.SurgeryOccurrenceNonOp.PatientSID,Surg.SurgeryOtherPostOpDiagnosis.PatientIEN,Surg.SurgeryOtherProcedure.PatientIEN,Surg.SurgeryOtherProcedureCPTModifier.PatientIEN,Surg.SurgeryOtherProcedureCPTModifier.PatientSID,Surg.SurgeryOtherProcedureDiagnosis.PatientIEN,Surg.SurgeryPOST.PatientIEN,Surg.SurgeryPostOpDiagnosis.PatientIEN,Surg.SurgeryPreOpDiagnosis.PatientIEN,Surg.SurgeryPreOpDiagnosis.PatientSID,Surg.SurgeryPrincipalAssociatedDiagnosis.PatientIEN,Surg.SurgeryPrincipalAssociatedProcedure.PatientIEN,Surg.SurgeryPrincipalCPTModifier.PatientIEN,Surg.SurgeryPrincipalDiagnosis.PatientIEN,Surg.SurgeryProcedureCPTModifier.PatientIEN,Surg.SurgeryProcedureDiagnosisCode.PatientIEN,Surg.SurgeryProcedureOccurrence.PatientIEN,Surg.SurgeryProcedureOccurrence.PatientSID,Surg.SurgeryRequiredBloodProducts.PatientIEN,Surg.SurgeryReturnCase.PatientIEN,Surg.SurgORCircSupport.PatientIEN,Surg.SurgORCircSupportTime.PatientIEN,Surg.SurgORCircSupportTime.PatientSID,Surg.SurgORScrubSupport.PatientIEN,Surg.SurgORScrubSupportTime.PatientIEN,Surg.SurgORScrubSupportTime.PatientSID</t>
   </si>
   <si>
-    <t>Procedure.CodeTableDetail.Procedure.Code</t>
+    <t>Procedure.Procedure[CodeTableDetail.Procedure].Code</t>
   </si>
   <si>
     <t>.playedRole[typeCode=USED].scoper.playedRole[typeCode=PAT]</t>
@@ -1801,7 +1801,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="109.51953125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="51.63671875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="52.02734375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="102.6171875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file PROSTHESIS INSTALLED (130.01) to us-core-implantable-device</t>
+    <t>This StructureDefinition contains the maps for VistA file PROSTHESIS INSTALLED (130.01) to us-core-implantable-device.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -637,7 +637,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>1348: source value from PROSTHESIS INSTALLED - IEN (130.01-.001)</t>
+    <t>1348: source value based on PROSTHESIS INSTALLED - IEN (130.01-.001)</t>
   </si>
   <si>
     <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
@@ -956,7 +956,7 @@
     <t>A name of the manufacturer.</t>
   </si>
   <si>
-    <t>1365: source value from PROSTHESIS INSTALLED - VENDOR (130.01-1)</t>
+    <t>1365: source value based on PROSTHESIS INSTALLED - VENDOR (130.01-1)</t>
   </si>
   <si>
     <t>SPatient.ImplantedProsthesis.ProsthesisVendor</t>
@@ -1078,7 +1078,7 @@
     <t>The name of the device.</t>
   </si>
   <si>
-    <t>1385: source value from PROSTHESIS INSTALLED - PROSTHESIS ITEM &gt; PROSTHESIS - NAME (130.01-.01 &gt; 131.9-.01)</t>
+    <t>1385: source value based on PROSTHESIS INSTALLED - PROSTHESIS ITEM &gt; PROSTHESIS - NAME (130.01-.01 &gt; 131.9-.01)</t>
   </si>
   <si>
     <t>SPatient.ImplantedProsthesis.ProsthesisIEN
@@ -1119,7 +1119,7 @@
     <t>The model number for the device.</t>
   </si>
   <si>
-    <t>1387: source value from PROSTHESIS INSTALLED - MODEL (130.01-2)</t>
+    <t>1387: source value based on PROSTHESIS INSTALLED - MODEL (130.01-2)</t>
   </si>
   <si>
     <t>SPatient.ImplantedProsthesis.ProsthesisModel</t>
@@ -1310,7 +1310,7 @@
     <t>If the device is implanted in a patient, then need to associate the device to the patient.</t>
   </si>
   <si>
-    <t>1399: reference from SURGERY - PATIENT (130-.01)</t>
+    <t>1399: reference based on SURGERY - PATIENT (130-.01)</t>
   </si>
   <si>
     <t>SPatient.ImplantedProsthesis.PatientIEN,SPatient.OperationsIndication.PatientIEN,Surg.AnesthesiaAgent.PatientIEN,Surg.AnesthesiaBlockSite.PatientIEN,Surg.AnesthesiaTechnique.PatientIEN,Surg.AnesthesiaTestDose.PatientIEN,Surg.ReferringPhysician.PatientIEN,Surg.ReferringPhysician.PatientSID,Surg.ReplacementFluidType.PatientIEN,Surg.ReplacementFluidType.PatientSID,Surg.SurgeryAssistant.PatientIEN,Surg.SurgeryAssistantOther.PatientIEN,Surg.SurgeryDelay.PatientIEN,Surg.SurgeryINTRA.PatientIEN,Surg.SurgeryIrrigation.PatientIEN,Surg.SurgeryIrrigation.PatientSID,Surg.SurgeryMedication.PatientIEN,Surg.SurgeryOccurrenceNonOp.PatientIEN,Surg.SurgeryOccurrenceNonOp.PatientSID,Surg.SurgeryOtherPostOpDiagnosis.PatientIEN,Surg.SurgeryOtherProcedure.PatientIEN,Surg.SurgeryOtherProcedureCPTModifier.PatientIEN,Surg.SurgeryOtherProcedureCPTModifier.PatientSID,Surg.SurgeryOtherProcedureDiagnosis.PatientIEN,Surg.SurgeryPOST.PatientIEN,Surg.SurgeryPostOpDiagnosis.PatientIEN,Surg.SurgeryPreOpDiagnosis.PatientIEN,Surg.SurgeryPreOpDiagnosis.PatientSID,Surg.SurgeryPrincipalAssociatedDiagnosis.PatientIEN,Surg.SurgeryPrincipalAssociatedProcedure.PatientIEN,Surg.SurgeryPrincipalCPTModifier.PatientIEN,Surg.SurgeryPrincipalDiagnosis.PatientIEN,Surg.SurgeryProcedureCPTModifier.PatientIEN,Surg.SurgeryProcedureDiagnosisCode.PatientIEN,Surg.SurgeryProcedureOccurrence.PatientIEN,Surg.SurgeryProcedureOccurrence.PatientSID,Surg.SurgeryRequiredBloodProducts.PatientIEN,Surg.SurgeryReturnCase.PatientIEN,Surg.SurgORCircSupport.PatientIEN,Surg.SurgORCircSupportTime.PatientIEN,Surg.SurgORCircSupportTime.PatientSID,Surg.SurgORScrubSupport.PatientIEN,Surg.SurgORScrubSupportTime.PatientIEN,Surg.SurgORScrubSupportTime.PatientSID</t>
@@ -1338,7 +1338,7 @@
     <t>An organization that is responsible for the provision and ongoing maintenance of the device.</t>
   </si>
   <si>
-    <t>1807: reference from SURGERY - DIVISION (130-50)</t>
+    <t>1807: reference based on SURGERY - DIVISION (130-50)</t>
   </si>
   <si>
     <t>Surg.SurgeryINTRA.InstitutionIEN,Surg.SurgeryPOST.InstitutionIEN</t>
@@ -1799,7 +1799,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="109.51953125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="113.61328125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="52.02734375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="102.6171875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2864" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2864" uniqueCount="454">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1051,9 +1051,6 @@
   </si>
   <si>
     <t>This represents the manufacturer's name of the device as provided by the device, from a UDI label, or by a person describing the Device.  This typically would be used when a person provides the name(s) or when the device represents one of the names available from DeviceDefinition.</t>
-  </si>
-  <si>
-    <t>1386: target not supported</t>
   </si>
   <si>
     <t>Device.deviceName.id</t>
@@ -6461,7 +6458,7 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>329</v>
+        <v>79</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>79</v>
@@ -6481,10 +6478,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6599,10 +6596,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6719,10 +6716,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6841,14 +6838,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6870,10 +6867,10 @@
         <v>153</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6924,7 +6921,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>87</v>
@@ -6939,10 +6936,10 @@
         <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>79</v>
@@ -6959,10 +6956,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6988,10 +6985,10 @@
         <v>107</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7003,7 +7000,7 @@
         <v>79</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>79</v>
@@ -7021,11 +7018,11 @@
         <v>169</v>
       </c>
       <c r="Y44" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="Z44" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="Z44" t="s" s="2">
-        <v>344</v>
-      </c>
       <c r="AA44" t="s" s="2">
         <v>79</v>
       </c>
@@ -7042,7 +7039,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>87</v>
@@ -7057,16 +7054,16 @@
         <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>238</v>
@@ -7077,10 +7074,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7106,10 +7103,10 @@
         <v>153</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7160,7 +7157,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7175,16 +7172,16 @@
         <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AL45" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AL45" t="s" s="2">
+      <c r="AM45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>238</v>
@@ -7195,10 +7192,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7224,10 +7221,10 @@
         <v>153</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>322</v>
@@ -7280,7 +7277,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7315,10 +7312,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7344,10 +7341,10 @@
         <v>175</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7359,7 +7356,7 @@
         <v>79</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="T47" t="s" s="2">
         <v>79</v>
@@ -7377,11 +7374,11 @@
         <v>180</v>
       </c>
       <c r="Y47" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="Z47" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="Z47" t="s" s="2">
-        <v>361</v>
-      </c>
       <c r="AA47" t="s" s="2">
         <v>79</v>
       </c>
@@ -7398,7 +7395,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7413,7 +7410,7 @@
         <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>79</v>
@@ -7433,10 +7430,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7462,10 +7459,10 @@
         <v>220</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7516,7 +7513,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7551,10 +7548,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7669,10 +7666,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7789,10 +7786,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7911,14 +7908,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7940,10 +7937,10 @@
         <v>175</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7994,7 +7991,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>87</v>
@@ -8029,10 +8026,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8058,10 +8055,10 @@
         <v>153</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8112,7 +8109,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8147,10 +8144,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8176,10 +8173,10 @@
         <v>220</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8230,7 +8227,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8265,10 +8262,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8383,10 +8380,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8503,10 +8500,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8625,14 +8622,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8654,10 +8651,10 @@
         <v>175</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8708,7 +8705,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8743,10 +8740,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8772,10 +8769,10 @@
         <v>145</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8826,7 +8823,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8861,10 +8858,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8890,10 +8887,10 @@
         <v>153</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8944,7 +8941,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>87</v>
@@ -8979,10 +8976,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9008,10 +9005,10 @@
         <v>220</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9062,7 +9059,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9097,10 +9094,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9215,10 +9212,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9335,10 +9332,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9457,10 +9454,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9486,10 +9483,10 @@
         <v>175</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9540,7 +9537,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>87</v>
@@ -9575,10 +9572,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9601,13 +9598,13 @@
         <v>79</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9658,7 +9655,7 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -9693,10 +9690,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9722,10 +9719,10 @@
         <v>175</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9776,7 +9773,7 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -9811,10 +9808,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9837,17 +9834,17 @@
         <v>79</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="M68" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>79</v>
@@ -9896,7 +9893,7 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -9911,19 +9908,19 @@
         <v>99</v>
       </c>
       <c r="AK68" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AL68" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="AL68" t="s" s="2">
+      <c r="AM68" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="AM68" t="s" s="2">
+      <c r="AN68" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="AN68" t="s" s="2">
+      <c r="AO68" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>79</v>
@@ -9931,10 +9928,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9957,13 +9954,13 @@
         <v>79</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10014,7 +10011,7 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10029,19 +10026,19 @@
         <v>99</v>
       </c>
       <c r="AK69" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AL69" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="AL69" t="s" s="2">
+      <c r="AM69" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="AM69" t="s" s="2">
+      <c r="AN69" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="AN69" t="s" s="2">
+      <c r="AO69" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>79</v>
@@ -10049,10 +10046,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10075,16 +10072,16 @@
         <v>79</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10134,7 +10131,7 @@
         <v>79</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10158,10 +10155,10 @@
         <v>79</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>79</v>
@@ -10169,10 +10166,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10195,17 +10192,17 @@
         <v>79</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="L71" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="L71" t="s" s="2">
+      <c r="M71" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>79</v>
@@ -10254,7 +10251,7 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10278,10 +10275,10 @@
         <v>79</v>
       </c>
       <c r="AN71" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AO71" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>79</v>
@@ -10289,10 +10286,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10318,13 +10315,13 @@
         <v>101</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10374,7 +10371,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10398,10 +10395,10 @@
         <v>79</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>79</v>
@@ -10409,10 +10406,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10435,13 +10432,13 @@
         <v>79</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="L73" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="M73" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10492,7 +10489,7 @@
         <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10516,7 +10513,7 @@
         <v>79</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>79</v>
@@ -10527,10 +10524,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10556,10 +10553,10 @@
         <v>175</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10610,7 +10607,7 @@
         <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -10645,10 +10642,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10671,13 +10668,13 @@
         <v>79</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="M75" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10728,7 +10725,7 @@
         <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
